--- a/Supermarket Data.xlsx
+++ b/Supermarket Data.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Desktop\Datasets\Supermarket\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03F3CB0-93F9-46AB-BD34-8CF9E03EB376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D64FAA-1D30-4D68-BC8C-63D68066B8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7083" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7079" uniqueCount="1071">
   <si>
     <t>Invoice ID</t>
   </si>
@@ -3843,7 +3843,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="112">
     <dxf>
       <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
@@ -3867,6 +3867,282 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
     <dxf>
       <numFmt numFmtId="25" formatCode="h:mm"/>
@@ -3956,12 +4232,12 @@
   <tableStyles count="3" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
     <tableStyle name="SlicerStyleLight1 2" pivot="0" table="0" count="10" xr9:uid="{B0A7CEAF-9A93-45F9-8577-603938C493F5}">
-      <tableStyleElement type="wholeTable" dxfId="19"/>
-      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="wholeTable" dxfId="111"/>
+      <tableStyleElement type="headerRow" dxfId="110"/>
     </tableStyle>
     <tableStyle name="Timeline Style 1" pivot="0" table="0" count="8" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" dxfId="17"/>
-      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="wholeTable" dxfId="109"/>
+      <tableStyleElement type="headerRow" dxfId="108"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -4519,19 +4795,19 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Health and beauty</c:v>
+                  <c:v>Home and lifestyle</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Home and lifestyle</c:v>
+                  <c:v>Sports and travel</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Fashion accessories</c:v>
+                  <c:v>Health and beauty</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Electronic accessories</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Sports and travel</c:v>
+                  <c:v>Fashion accessories</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>Food and beverages</c:v>
@@ -4546,22 +4822,22 @@
                 <c:formatCode>_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>49193.739000000016</c:v>
+                  <c:v>13895.553</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53861.913000000008</c:v>
+                  <c:v>15761.928</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54305.894999999997</c:v>
+                  <c:v>16615.326000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>54337.531500000005</c:v>
+                  <c:v>18968.974500000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55122.826499999996</c:v>
+                  <c:v>21560.070000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>56144.844000000005</c:v>
+                  <c:v>23766.854999999992</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4932,16 +5208,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$D$8:$D$11</c:f>
+              <c:f>Sheet1!$D$8:$D$9</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>A</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>B</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>C</c:v>
                 </c:pt>
               </c:strCache>
@@ -4949,18 +5219,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$8:$E$11</c:f>
+              <c:f>Sheet1!$E$8:$E$9</c:f>
               <c:numCache>
                 <c:formatCode>_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5057.1605000000418</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5057.0320000000356</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5265.1764999999432</c:v>
+                  <c:v>5265.1764999999577</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5404,35 +5668,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$19:$A$22</c:f>
+              <c:f>Sheet1!$A$19:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Naypyitaw</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Yangon</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Mandalay</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$19:$B$22</c:f>
+              <c:f>Sheet1!$B$19:$B$20</c:f>
               <c:numCache>
                 <c:formatCode>_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>110568.70649999994</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>106200.37050000011</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>106197.67199999996</c:v>
+                  <c:v>110568.7065</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5874,10 +6126,10 @@
                 <c:formatCode>_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>164223.44400000002</c:v>
+                  <c:v>56881.282499999994</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>158743.30500000005</c:v>
+                  <c:v>53687.423999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7002,13 +7254,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>344</c:v>
+                  <c:v>124</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>311</c:v>
+                  <c:v>98</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>345</c:v>
+                  <c:v>106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7092,16 +7344,9 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:noFill/>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -7494,13 +7739,13 @@
                 <c:formatCode>_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>116291.86800000005</c:v>
+                  <c:v>40434.681000000004</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>97219.373999999967</c:v>
+                  <c:v>32934.982499999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>109455.50700000004</c:v>
+                  <c:v>37199.042999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11316,15 +11561,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>253443</xdr:colOff>
+      <xdr:colOff>263470</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>173543</xdr:rowOff>
+      <xdr:rowOff>113385</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>34879</xdr:colOff>
+      <xdr:colOff>44906</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>128339</xdr:rowOff>
+      <xdr:rowOff>68181</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11339,8 +11584,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3315050" y="554543"/>
-          <a:ext cx="1618400" cy="907296"/>
+          <a:off x="3321496" y="494385"/>
+          <a:ext cx="1616252" cy="907296"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11714,13 +11959,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>238546</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>152949</xdr:rowOff>
+      <xdr:rowOff>48279</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>159387</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>117999</xdr:rowOff>
+      <xdr:rowOff>13329</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11735,8 +11980,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4524796" y="3772449"/>
-          <a:ext cx="2982448" cy="1870050"/>
+          <a:off x="4488161" y="3628004"/>
+          <a:ext cx="2956281" cy="1849116"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12342,13 +12587,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>238547</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>136071</xdr:rowOff>
+      <xdr:rowOff>31400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>176894</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>40822</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>124557</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12378,15 +12623,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>435429</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>103413</xdr:rowOff>
+      <xdr:colOff>581967</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>155747</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>130631</xdr:colOff>
+      <xdr:colOff>277169</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
+      <xdr:rowOff>27214</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -12401,8 +12646,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4721679" y="3722913"/>
-          <a:ext cx="2756809" cy="250373"/>
+          <a:off x="4831582" y="3547066"/>
+          <a:ext cx="2730642" cy="248280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12615,7 +12860,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t> $322,966.75 </a:t>
+            <a:t> $110,568.71 </a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1400" b="1"/>
         </a:p>
@@ -12626,13 +12871,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>560614</xdr:colOff>
+      <xdr:colOff>270711</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>166007</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>367392</xdr:colOff>
+      <xdr:colOff>591551</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
@@ -12649,8 +12894,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3622221" y="928007"/>
-          <a:ext cx="1031421" cy="367393"/>
+          <a:off x="3328737" y="928007"/>
+          <a:ext cx="1544051" cy="367393"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12687,7 +12932,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t> $15,379.37 </a:t>
+            <a:t> $5,265.18 </a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1400" b="1"/>
         </a:p>
@@ -12759,7 +13004,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1000</a:t>
+            <a:t>328</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1400" b="1"/>
         </a:p>
@@ -12831,7 +13076,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>6.97</a:t>
+            <a:t>7.07</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1400" b="1"/>
         </a:p>
@@ -12903,7 +13148,7 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>5510</a:t>
+            <a:t>1831</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1400" b="1"/>
         </a:p>
@@ -13009,8 +13254,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3186795" y="533400"/>
-          <a:ext cx="2027464" cy="272143"/>
+          <a:off x="3183214" y="533400"/>
+          <a:ext cx="2025316" cy="272143"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -31737,7 +31982,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B09E73DD-A55F-4FBB-A10E-AE59B2970949}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="D7:E11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="D7:E9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField showAll="0">
       <items count="1001">
@@ -32746,8 +32991,8 @@
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="4">
-        <item x="0"/>
-        <item x="2"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -32917,13 +33162,7 @@
   <rowFields count="1">
     <field x="1"/>
   </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
+  <rowItems count="2">
     <i>
       <x v="2"/>
     </i>
@@ -32962,7 +33201,7 @@
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{21F00A60-A37C-4B3B-8BF4-D02C7DB8A8AE}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
-  <location ref="A18:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A18:B20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField showAll="0">
       <items count="1001">
@@ -33971,8 +34210,8 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="4">
-        <item x="0"/>
-        <item x="2"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -34151,15 +34390,9 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="2">
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -34172,7 +34405,7 @@
     <dataField name="Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="12">
+    <format dxfId="104">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
@@ -34213,6 +34446,3745 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CBF87619-36E8-492C-98AD-E06666849A62}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="D16:E20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField showAll="0">
+      <items count="1001">
+        <item x="162"/>
+        <item x="867"/>
+        <item x="778"/>
+        <item x="776"/>
+        <item x="683"/>
+        <item x="169"/>
+        <item x="56"/>
+        <item x="67"/>
+        <item x="824"/>
+        <item x="400"/>
+        <item x="255"/>
+        <item x="891"/>
+        <item x="881"/>
+        <item x="352"/>
+        <item x="905"/>
+        <item x="59"/>
+        <item x="775"/>
+        <item x="366"/>
+        <item x="3"/>
+        <item x="597"/>
+        <item x="864"/>
+        <item x="849"/>
+        <item x="272"/>
+        <item x="585"/>
+        <item x="36"/>
+        <item x="679"/>
+        <item x="180"/>
+        <item x="643"/>
+        <item x="938"/>
+        <item x="412"/>
+        <item x="45"/>
+        <item x="523"/>
+        <item x="654"/>
+        <item x="562"/>
+        <item x="554"/>
+        <item x="625"/>
+        <item x="345"/>
+        <item x="280"/>
+        <item x="737"/>
+        <item x="888"/>
+        <item x="442"/>
+        <item x="290"/>
+        <item x="982"/>
+        <item x="177"/>
+        <item x="212"/>
+        <item x="242"/>
+        <item x="268"/>
+        <item x="28"/>
+        <item x="899"/>
+        <item x="983"/>
+        <item x="493"/>
+        <item x="725"/>
+        <item x="653"/>
+        <item x="630"/>
+        <item x="31"/>
+        <item x="344"/>
+        <item x="258"/>
+        <item x="911"/>
+        <item x="979"/>
+        <item x="862"/>
+        <item x="93"/>
+        <item x="596"/>
+        <item x="383"/>
+        <item x="264"/>
+        <item x="875"/>
+        <item x="641"/>
+        <item x="978"/>
+        <item x="759"/>
+        <item x="234"/>
+        <item x="854"/>
+        <item x="51"/>
+        <item x="707"/>
+        <item x="100"/>
+        <item x="873"/>
+        <item x="655"/>
+        <item x="965"/>
+        <item x="542"/>
+        <item x="688"/>
+        <item x="391"/>
+        <item x="315"/>
+        <item x="727"/>
+        <item x="560"/>
+        <item x="176"/>
+        <item x="701"/>
+        <item x="865"/>
+        <item x="921"/>
+        <item x="311"/>
+        <item x="696"/>
+        <item x="379"/>
+        <item x="634"/>
+        <item x="712"/>
+        <item x="34"/>
+        <item x="417"/>
+        <item x="821"/>
+        <item x="908"/>
+        <item x="705"/>
+        <item x="454"/>
+        <item x="635"/>
+        <item x="127"/>
+        <item x="27"/>
+        <item x="984"/>
+        <item x="513"/>
+        <item x="809"/>
+        <item x="101"/>
+        <item x="667"/>
+        <item x="819"/>
+        <item x="130"/>
+        <item x="702"/>
+        <item x="443"/>
+        <item x="967"/>
+        <item x="693"/>
+        <item x="738"/>
+        <item x="556"/>
+        <item x="425"/>
+        <item x="63"/>
+        <item x="774"/>
+        <item x="954"/>
+        <item x="772"/>
+        <item x="370"/>
+        <item x="579"/>
+        <item x="511"/>
+        <item x="750"/>
+        <item x="552"/>
+        <item x="111"/>
+        <item x="728"/>
+        <item x="295"/>
+        <item x="236"/>
+        <item x="103"/>
+        <item x="549"/>
+        <item x="224"/>
+        <item x="153"/>
+        <item x="969"/>
+        <item x="243"/>
+        <item x="559"/>
+        <item x="122"/>
+        <item x="600"/>
+        <item x="518"/>
+        <item x="805"/>
+        <item x="976"/>
+        <item x="826"/>
+        <item x="91"/>
+        <item x="115"/>
+        <item x="1"/>
+        <item x="925"/>
+        <item x="287"/>
+        <item x="25"/>
+        <item x="314"/>
+        <item x="589"/>
+        <item x="112"/>
+        <item x="43"/>
+        <item x="68"/>
+        <item x="35"/>
+        <item x="469"/>
+        <item x="995"/>
+        <item x="461"/>
+        <item x="858"/>
+        <item x="166"/>
+        <item x="935"/>
+        <item x="446"/>
+        <item x="533"/>
+        <item x="402"/>
+        <item x="114"/>
+        <item x="830"/>
+        <item x="734"/>
+        <item x="149"/>
+        <item x="144"/>
+        <item x="220"/>
+        <item x="572"/>
+        <item x="568"/>
+        <item x="138"/>
+        <item x="685"/>
+        <item x="675"/>
+        <item x="54"/>
+        <item x="543"/>
+        <item x="932"/>
+        <item x="410"/>
+        <item x="481"/>
+        <item x="920"/>
+        <item x="730"/>
+        <item x="170"/>
+        <item x="758"/>
+        <item x="656"/>
+        <item x="13"/>
+        <item x="265"/>
+        <item x="369"/>
+        <item x="408"/>
+        <item x="960"/>
+        <item x="807"/>
+        <item x="436"/>
+        <item x="598"/>
+        <item x="715"/>
+        <item x="371"/>
+        <item x="148"/>
+        <item x="76"/>
+        <item x="793"/>
+        <item x="207"/>
+        <item x="691"/>
+        <item x="420"/>
+        <item x="988"/>
+        <item x="415"/>
+        <item x="713"/>
+        <item x="124"/>
+        <item x="233"/>
+        <item x="426"/>
+        <item x="839"/>
+        <item x="422"/>
+        <item x="364"/>
+        <item x="37"/>
+        <item x="22"/>
+        <item x="644"/>
+        <item x="677"/>
+        <item x="161"/>
+        <item x="325"/>
+        <item x="823"/>
+        <item x="611"/>
+        <item x="500"/>
+        <item x="586"/>
+        <item x="292"/>
+        <item x="223"/>
+        <item x="156"/>
+        <item x="141"/>
+        <item x="40"/>
+        <item x="503"/>
+        <item x="557"/>
+        <item x="288"/>
+        <item x="190"/>
+        <item x="613"/>
+        <item x="60"/>
+        <item x="306"/>
+        <item x="192"/>
+        <item x="526"/>
+        <item x="430"/>
+        <item x="74"/>
+        <item x="530"/>
+        <item x="754"/>
+        <item x="836"/>
+        <item x="380"/>
+        <item x="230"/>
+        <item x="253"/>
+        <item x="508"/>
+        <item x="116"/>
+        <item x="883"/>
+        <item x="841"/>
+        <item x="448"/>
+        <item x="729"/>
+        <item x="15"/>
+        <item x="20"/>
+        <item x="444"/>
+        <item x="423"/>
+        <item x="590"/>
+        <item x="996"/>
+        <item x="689"/>
+        <item x="186"/>
+        <item x="483"/>
+        <item x="951"/>
+        <item x="782"/>
+        <item x="298"/>
+        <item x="157"/>
+        <item x="629"/>
+        <item x="393"/>
+        <item x="538"/>
+        <item x="882"/>
+        <item x="910"/>
+        <item x="749"/>
+        <item x="7"/>
+        <item x="396"/>
+        <item x="171"/>
+        <item x="859"/>
+        <item x="293"/>
+        <item x="608"/>
+        <item x="89"/>
+        <item x="637"/>
+        <item x="19"/>
+        <item x="217"/>
+        <item x="463"/>
+        <item x="354"/>
+        <item x="681"/>
+        <item x="926"/>
+        <item x="660"/>
+        <item x="801"/>
+        <item x="961"/>
+        <item x="429"/>
+        <item x="886"/>
+        <item x="458"/>
+        <item x="462"/>
+        <item x="50"/>
+        <item x="616"/>
+        <item x="18"/>
+        <item x="944"/>
+        <item x="38"/>
+        <item x="599"/>
+        <item x="123"/>
+        <item x="142"/>
+        <item x="536"/>
+        <item x="582"/>
+        <item x="527"/>
+        <item x="575"/>
+        <item x="471"/>
+        <item x="329"/>
+        <item x="179"/>
+        <item x="571"/>
+        <item x="832"/>
+        <item x="541"/>
+        <item x="437"/>
+        <item x="744"/>
+        <item x="399"/>
+        <item x="238"/>
+        <item x="62"/>
+        <item x="998"/>
+        <item x="510"/>
+        <item x="609"/>
+        <item x="10"/>
+        <item x="42"/>
+        <item x="137"/>
+        <item x="573"/>
+        <item x="6"/>
+        <item x="555"/>
+        <item x="539"/>
+        <item x="583"/>
+        <item x="798"/>
+        <item x="84"/>
+        <item x="866"/>
+        <item x="937"/>
+        <item x="86"/>
+        <item x="638"/>
+        <item x="963"/>
+        <item x="949"/>
+        <item x="12"/>
+        <item x="820"/>
+        <item x="256"/>
+        <item x="650"/>
+        <item x="46"/>
+        <item x="682"/>
+        <item x="21"/>
+        <item x="409"/>
+        <item x="694"/>
+        <item x="322"/>
+        <item x="602"/>
+        <item x="742"/>
+        <item x="4"/>
+        <item x="948"/>
+        <item x="339"/>
+        <item x="985"/>
+        <item x="584"/>
+        <item x="244"/>
+        <item x="277"/>
+        <item x="900"/>
+        <item x="340"/>
+        <item x="119"/>
+        <item x="588"/>
+        <item x="811"/>
+        <item x="259"/>
+        <item x="77"/>
+        <item x="69"/>
+        <item x="373"/>
+        <item x="959"/>
+        <item x="736"/>
+        <item x="506"/>
+        <item x="767"/>
+        <item x="222"/>
+        <item x="890"/>
+        <item x="745"/>
+        <item x="580"/>
+        <item x="445"/>
+        <item x="70"/>
+        <item x="441"/>
+        <item x="388"/>
+        <item x="204"/>
+        <item x="690"/>
+        <item x="304"/>
+        <item x="927"/>
+        <item x="55"/>
+        <item x="553"/>
+        <item x="349"/>
+        <item x="188"/>
+        <item x="791"/>
+        <item x="154"/>
+        <item x="799"/>
+        <item x="498"/>
+        <item x="785"/>
+        <item x="472"/>
+        <item x="757"/>
+        <item x="178"/>
+        <item x="569"/>
+        <item x="668"/>
+        <item x="851"/>
+        <item x="897"/>
+        <item x="762"/>
+        <item x="305"/>
+        <item x="515"/>
+        <item x="174"/>
+        <item x="343"/>
+        <item x="829"/>
+        <item x="232"/>
+        <item x="720"/>
+        <item x="633"/>
+        <item x="199"/>
+        <item x="499"/>
+        <item x="620"/>
+        <item x="610"/>
+        <item x="374"/>
+        <item x="159"/>
+        <item x="313"/>
+        <item x="163"/>
+        <item x="516"/>
+        <item x="202"/>
+        <item x="834"/>
+        <item x="316"/>
+        <item x="957"/>
+        <item x="989"/>
+        <item x="289"/>
+        <item x="928"/>
+        <item x="936"/>
+        <item x="341"/>
+        <item x="724"/>
+        <item x="181"/>
+        <item x="531"/>
+        <item x="621"/>
+        <item x="494"/>
+        <item x="191"/>
+        <item x="485"/>
+        <item x="733"/>
+        <item x="303"/>
+        <item x="466"/>
+        <item x="346"/>
+        <item x="726"/>
+        <item x="333"/>
+        <item x="614"/>
+        <item x="796"/>
+        <item x="581"/>
+        <item x="709"/>
+        <item x="300"/>
+        <item x="263"/>
+        <item x="971"/>
+        <item x="878"/>
+        <item x="241"/>
+        <item x="943"/>
+        <item x="449"/>
+        <item x="440"/>
+        <item x="906"/>
+        <item x="521"/>
+        <item x="741"/>
+        <item x="972"/>
+        <item x="447"/>
+        <item x="912"/>
+        <item x="358"/>
+        <item x="924"/>
+        <item x="746"/>
+        <item x="779"/>
+        <item x="933"/>
+        <item x="145"/>
+        <item x="576"/>
+        <item x="914"/>
+        <item x="432"/>
+        <item x="540"/>
+        <item x="885"/>
+        <item x="363"/>
+        <item x="381"/>
+        <item x="228"/>
+        <item x="221"/>
+        <item x="367"/>
+        <item x="783"/>
+        <item x="595"/>
+        <item x="464"/>
+        <item x="773"/>
+        <item x="362"/>
+        <item x="414"/>
+        <item x="802"/>
+        <item x="274"/>
+        <item x="816"/>
+        <item x="239"/>
+        <item x="110"/>
+        <item x="82"/>
+        <item x="717"/>
+        <item x="134"/>
+        <item x="604"/>
+        <item x="476"/>
+        <item x="748"/>
+        <item x="143"/>
+        <item x="424"/>
+        <item x="945"/>
+        <item x="282"/>
+        <item x="880"/>
+        <item x="659"/>
+        <item x="484"/>
+        <item x="840"/>
+        <item x="789"/>
+        <item x="285"/>
+        <item x="815"/>
+        <item x="939"/>
+        <item x="934"/>
+        <item x="475"/>
+        <item x="514"/>
+        <item x="950"/>
+        <item x="88"/>
+        <item x="165"/>
+        <item x="901"/>
+        <item x="615"/>
+        <item x="491"/>
+        <item x="684"/>
+        <item x="72"/>
+        <item x="504"/>
+        <item x="94"/>
+        <item x="308"/>
+        <item x="564"/>
+        <item x="784"/>
+        <item x="665"/>
+        <item x="977"/>
+        <item x="517"/>
+        <item x="913"/>
+        <item x="281"/>
+        <item x="761"/>
+        <item x="385"/>
+        <item x="276"/>
+        <item x="335"/>
+        <item x="833"/>
+        <item x="680"/>
+        <item x="11"/>
+        <item x="245"/>
+        <item x="973"/>
+        <item x="348"/>
+        <item x="310"/>
+        <item x="457"/>
+        <item x="863"/>
+        <item x="524"/>
+        <item x="781"/>
+        <item x="278"/>
+        <item x="828"/>
+        <item x="548"/>
+        <item x="240"/>
+        <item x="480"/>
+        <item x="547"/>
+        <item x="390"/>
+        <item x="201"/>
+        <item x="607"/>
+        <item x="872"/>
+        <item x="904"/>
+        <item x="231"/>
+        <item x="743"/>
+        <item x="164"/>
+        <item x="884"/>
+        <item x="218"/>
+        <item x="843"/>
+        <item x="24"/>
+        <item x="129"/>
+        <item x="438"/>
+        <item x="574"/>
+        <item x="102"/>
+        <item x="987"/>
+        <item x="357"/>
+        <item x="467"/>
+        <item x="41"/>
+        <item x="673"/>
+        <item x="488"/>
+        <item x="195"/>
+        <item x="496"/>
+        <item x="966"/>
+        <item x="291"/>
+        <item x="808"/>
+        <item x="606"/>
+        <item x="216"/>
+        <item x="592"/>
+        <item x="657"/>
+        <item x="392"/>
+        <item x="651"/>
+        <item x="323"/>
+        <item x="284"/>
+        <item x="353"/>
+        <item x="90"/>
+        <item x="810"/>
+        <item x="275"/>
+        <item x="332"/>
+        <item x="453"/>
+        <item x="147"/>
+        <item x="411"/>
+        <item x="825"/>
+        <item x="267"/>
+        <item x="301"/>
+        <item x="208"/>
+        <item x="501"/>
+        <item x="49"/>
+        <item x="647"/>
+        <item x="431"/>
+        <item x="952"/>
+        <item x="139"/>
+        <item x="479"/>
+        <item x="672"/>
+        <item x="956"/>
+        <item x="359"/>
+        <item x="551"/>
+        <item x="535"/>
+        <item x="227"/>
+        <item x="871"/>
+        <item x="151"/>
+        <item x="294"/>
+        <item x="594"/>
+        <item x="751"/>
+        <item x="846"/>
+        <item x="184"/>
+        <item x="404"/>
+        <item x="763"/>
+        <item x="108"/>
+        <item x="670"/>
+        <item x="632"/>
+        <item x="133"/>
+        <item x="577"/>
+        <item x="723"/>
+        <item x="962"/>
+        <item x="765"/>
+        <item x="189"/>
+        <item x="286"/>
+        <item x="95"/>
+        <item x="33"/>
+        <item x="512"/>
+        <item x="378"/>
+        <item x="902"/>
+        <item x="389"/>
+        <item x="135"/>
+        <item x="624"/>
+        <item x="477"/>
+        <item x="519"/>
+        <item x="991"/>
+        <item x="509"/>
+        <item x="317"/>
+        <item x="247"/>
+        <item x="968"/>
+        <item x="361"/>
+        <item x="795"/>
+        <item x="200"/>
+        <item x="735"/>
+        <item x="892"/>
+        <item x="492"/>
+        <item x="877"/>
+        <item x="173"/>
+        <item x="150"/>
+        <item x="522"/>
+        <item x="636"/>
+        <item x="360"/>
+        <item x="368"/>
+        <item x="52"/>
+        <item x="433"/>
+        <item x="44"/>
+        <item x="806"/>
+        <item x="502"/>
+        <item x="321"/>
+        <item x="909"/>
+        <item x="700"/>
+        <item x="489"/>
+        <item x="106"/>
+        <item x="627"/>
+        <item x="780"/>
+        <item x="107"/>
+        <item x="868"/>
+        <item x="2"/>
+        <item x="495"/>
+        <item x="356"/>
+        <item x="338"/>
+        <item x="87"/>
+        <item x="273"/>
+        <item x="331"/>
+        <item x="731"/>
+        <item x="57"/>
+        <item x="831"/>
+        <item x="23"/>
+        <item x="919"/>
+        <item x="120"/>
+        <item x="460"/>
+        <item x="704"/>
+        <item x="32"/>
+        <item x="193"/>
+        <item x="663"/>
+        <item x="930"/>
+        <item x="619"/>
+        <item x="603"/>
+        <item x="118"/>
+        <item x="671"/>
+        <item x="537"/>
+        <item x="113"/>
+        <item x="235"/>
+        <item x="546"/>
+        <item x="687"/>
+        <item x="678"/>
+        <item x="320"/>
+        <item x="26"/>
+        <item x="427"/>
+        <item x="401"/>
+        <item x="567"/>
+        <item x="790"/>
+        <item x="755"/>
+        <item x="994"/>
+        <item x="631"/>
+        <item x="262"/>
+        <item x="213"/>
+        <item x="16"/>
+        <item x="852"/>
+        <item x="121"/>
+        <item x="117"/>
+        <item x="838"/>
+        <item x="251"/>
+        <item x="384"/>
+        <item x="128"/>
+        <item x="747"/>
+        <item x="8"/>
+        <item x="639"/>
+        <item x="375"/>
+        <item x="283"/>
+        <item x="125"/>
+        <item x="48"/>
+        <item x="837"/>
+        <item x="622"/>
+        <item x="206"/>
+        <item x="482"/>
+        <item x="813"/>
+        <item x="947"/>
+        <item x="474"/>
+        <item x="211"/>
+        <item x="721"/>
+        <item x="669"/>
+        <item x="146"/>
+        <item x="490"/>
+        <item x="271"/>
+        <item x="167"/>
+        <item x="692"/>
+        <item x="386"/>
+        <item x="993"/>
+        <item x="337"/>
+        <item x="9"/>
+        <item x="640"/>
+        <item x="587"/>
+        <item x="132"/>
+        <item x="413"/>
+        <item x="565"/>
+        <item x="198"/>
+        <item x="5"/>
+        <item x="895"/>
+        <item x="136"/>
+        <item x="545"/>
+        <item x="478"/>
+        <item x="794"/>
+        <item x="941"/>
+        <item x="788"/>
+        <item x="254"/>
+        <item x="318"/>
+        <item x="105"/>
+        <item x="645"/>
+        <item x="770"/>
+        <item x="486"/>
+        <item x="456"/>
+        <item x="768"/>
+        <item x="558"/>
+        <item x="664"/>
+        <item x="893"/>
+        <item x="104"/>
+        <item x="915"/>
+        <item x="566"/>
+        <item x="327"/>
+        <item x="525"/>
+        <item x="940"/>
+        <item x="229"/>
+        <item x="916"/>
+        <item x="407"/>
+        <item x="898"/>
+        <item x="387"/>
+        <item x="662"/>
+        <item x="347"/>
+        <item x="395"/>
+        <item x="505"/>
+        <item x="997"/>
+        <item x="452"/>
+        <item x="47"/>
+        <item x="296"/>
+        <item x="980"/>
+        <item x="711"/>
+        <item x="703"/>
+        <item x="257"/>
+        <item x="459"/>
+        <item x="85"/>
+        <item x="328"/>
+        <item x="372"/>
+        <item x="269"/>
+        <item x="473"/>
+        <item x="140"/>
+        <item x="187"/>
+        <item x="406"/>
+        <item x="75"/>
+        <item x="99"/>
+        <item x="740"/>
+        <item x="172"/>
+        <item x="520"/>
+        <item x="302"/>
+        <item x="714"/>
+        <item x="874"/>
+        <item x="649"/>
+        <item x="421"/>
+        <item x="428"/>
+        <item x="652"/>
+        <item x="158"/>
+        <item x="377"/>
+        <item x="297"/>
+        <item x="451"/>
+        <item x="792"/>
+        <item x="974"/>
+        <item x="419"/>
+        <item x="992"/>
+        <item x="970"/>
+        <item x="468"/>
+        <item x="324"/>
+        <item x="225"/>
+        <item x="152"/>
+        <item x="550"/>
+        <item x="857"/>
+        <item x="205"/>
+        <item x="917"/>
+        <item x="416"/>
+        <item x="0"/>
+        <item x="800"/>
+        <item x="699"/>
+        <item x="435"/>
+        <item x="676"/>
+        <item x="237"/>
+        <item x="79"/>
+        <item x="732"/>
+        <item x="931"/>
+        <item x="803"/>
+        <item x="771"/>
+        <item x="708"/>
+        <item x="827"/>
+        <item x="397"/>
+        <item x="563"/>
+        <item x="879"/>
+        <item x="986"/>
+        <item x="17"/>
+        <item x="96"/>
+        <item x="470"/>
+        <item x="455"/>
+        <item x="686"/>
+        <item x="856"/>
+        <item x="753"/>
+        <item x="722"/>
+        <item x="918"/>
+        <item x="39"/>
+        <item x="814"/>
+        <item x="53"/>
+        <item x="646"/>
+        <item x="299"/>
+        <item x="666"/>
+        <item x="896"/>
+        <item x="155"/>
+        <item x="270"/>
+        <item x="953"/>
+        <item x="822"/>
+        <item x="249"/>
+        <item x="756"/>
+        <item x="710"/>
+        <item x="319"/>
+        <item x="83"/>
+        <item x="764"/>
+        <item x="591"/>
+        <item x="718"/>
+        <item x="612"/>
+        <item x="219"/>
+        <item x="787"/>
+        <item x="398"/>
+        <item x="642"/>
+        <item x="964"/>
+        <item x="487"/>
+        <item x="71"/>
+        <item x="168"/>
+        <item x="578"/>
+        <item x="248"/>
+        <item x="695"/>
+        <item x="766"/>
+        <item x="215"/>
+        <item x="131"/>
+        <item x="307"/>
+        <item x="61"/>
+        <item x="845"/>
+        <item x="739"/>
+        <item x="752"/>
+        <item x="835"/>
+        <item x="266"/>
+        <item x="981"/>
+        <item x="942"/>
+        <item x="439"/>
+        <item x="674"/>
+        <item x="894"/>
+        <item x="812"/>
+        <item x="326"/>
+        <item x="626"/>
+        <item x="658"/>
+        <item x="58"/>
+        <item x="209"/>
+        <item x="261"/>
+        <item x="719"/>
+        <item x="183"/>
+        <item x="929"/>
+        <item x="697"/>
+        <item x="175"/>
+        <item x="528"/>
+        <item x="529"/>
+        <item x="618"/>
+        <item x="279"/>
+        <item x="14"/>
+        <item x="78"/>
+        <item x="605"/>
+        <item x="194"/>
+        <item x="403"/>
+        <item x="804"/>
+        <item x="817"/>
+        <item x="365"/>
+        <item x="706"/>
+        <item x="351"/>
+        <item x="570"/>
+        <item x="334"/>
+        <item x="226"/>
+        <item x="434"/>
+        <item x="922"/>
+        <item x="66"/>
+        <item x="617"/>
+        <item x="861"/>
+        <item x="544"/>
+        <item x="73"/>
+        <item x="661"/>
+        <item x="760"/>
+        <item x="376"/>
+        <item x="850"/>
+        <item x="250"/>
+        <item x="848"/>
+        <item x="955"/>
+        <item x="81"/>
+        <item x="418"/>
+        <item x="196"/>
+        <item x="309"/>
+        <item x="29"/>
+        <item x="860"/>
+        <item x="999"/>
+        <item x="260"/>
+        <item x="182"/>
+        <item x="907"/>
+        <item x="623"/>
+        <item x="869"/>
+        <item x="64"/>
+        <item x="197"/>
+        <item x="628"/>
+        <item x="716"/>
+        <item x="532"/>
+        <item x="648"/>
+        <item x="946"/>
+        <item x="842"/>
+        <item x="350"/>
+        <item x="109"/>
+        <item x="507"/>
+        <item x="847"/>
+        <item x="497"/>
+        <item x="797"/>
+        <item x="903"/>
+        <item x="98"/>
+        <item x="246"/>
+        <item x="853"/>
+        <item x="561"/>
+        <item x="958"/>
+        <item x="698"/>
+        <item x="382"/>
+        <item x="330"/>
+        <item x="818"/>
+        <item x="126"/>
+        <item x="80"/>
+        <item x="312"/>
+        <item x="97"/>
+        <item x="30"/>
+        <item x="870"/>
+        <item x="92"/>
+        <item x="342"/>
+        <item x="777"/>
+        <item x="203"/>
+        <item x="65"/>
+        <item x="465"/>
+        <item x="593"/>
+        <item x="889"/>
+        <item x="601"/>
+        <item x="405"/>
+        <item x="252"/>
+        <item x="975"/>
+        <item x="887"/>
+        <item x="394"/>
+        <item x="876"/>
+        <item x="990"/>
+        <item x="769"/>
+        <item x="786"/>
+        <item x="923"/>
+        <item x="210"/>
+        <item x="355"/>
+        <item x="450"/>
+        <item x="214"/>
+        <item x="534"/>
+        <item x="160"/>
+        <item x="855"/>
+        <item x="185"/>
+        <item x="844"/>
+        <item x="336"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="1"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="90">
+        <item x="17"/>
+        <item x="56"/>
+        <item x="75"/>
+        <item x="72"/>
+        <item x="0"/>
+        <item x="47"/>
+        <item x="27"/>
+        <item x="66"/>
+        <item x="51"/>
+        <item x="8"/>
+        <item x="83"/>
+        <item x="52"/>
+        <item x="50"/>
+        <item x="78"/>
+        <item x="15"/>
+        <item x="65"/>
+        <item x="29"/>
+        <item x="68"/>
+        <item x="64"/>
+        <item x="40"/>
+        <item x="18"/>
+        <item x="49"/>
+        <item x="54"/>
+        <item x="46"/>
+        <item x="25"/>
+        <item x="53"/>
+        <item x="3"/>
+        <item x="26"/>
+        <item x="71"/>
+        <item x="74"/>
+        <item x="82"/>
+        <item x="60"/>
+        <item x="30"/>
+        <item x="36"/>
+        <item x="87"/>
+        <item x="63"/>
+        <item x="10"/>
+        <item x="13"/>
+        <item x="4"/>
+        <item x="57"/>
+        <item x="34"/>
+        <item x="48"/>
+        <item x="12"/>
+        <item x="77"/>
+        <item x="44"/>
+        <item x="42"/>
+        <item x="69"/>
+        <item x="21"/>
+        <item x="67"/>
+        <item x="88"/>
+        <item x="9"/>
+        <item x="81"/>
+        <item x="70"/>
+        <item x="55"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="84"/>
+        <item x="33"/>
+        <item x="38"/>
+        <item x="59"/>
+        <item x="22"/>
+        <item x="2"/>
+        <item x="31"/>
+        <item x="19"/>
+        <item x="43"/>
+        <item x="37"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="24"/>
+        <item x="16"/>
+        <item x="41"/>
+        <item x="45"/>
+        <item x="86"/>
+        <item x="20"/>
+        <item x="32"/>
+        <item x="85"/>
+        <item x="79"/>
+        <item x="35"/>
+        <item x="80"/>
+        <item x="76"/>
+        <item x="23"/>
+        <item x="28"/>
+        <item x="62"/>
+        <item x="5"/>
+        <item x="58"/>
+        <item x="39"/>
+        <item x="61"/>
+        <item x="14"/>
+        <item x="73"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="20" showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0" countASubtotal="1">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="countA"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Payment" fld="11" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="7" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B3E162D0-00BF-4097-8067-334C9A57E3BD}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="G16:H19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField showAll="0">
+      <items count="1001">
+        <item x="162"/>
+        <item x="867"/>
+        <item x="778"/>
+        <item x="776"/>
+        <item x="683"/>
+        <item x="169"/>
+        <item x="56"/>
+        <item x="67"/>
+        <item x="824"/>
+        <item x="400"/>
+        <item x="255"/>
+        <item x="891"/>
+        <item x="881"/>
+        <item x="352"/>
+        <item x="905"/>
+        <item x="59"/>
+        <item x="775"/>
+        <item x="366"/>
+        <item x="3"/>
+        <item x="597"/>
+        <item x="864"/>
+        <item x="849"/>
+        <item x="272"/>
+        <item x="585"/>
+        <item x="36"/>
+        <item x="679"/>
+        <item x="180"/>
+        <item x="643"/>
+        <item x="938"/>
+        <item x="412"/>
+        <item x="45"/>
+        <item x="523"/>
+        <item x="654"/>
+        <item x="562"/>
+        <item x="554"/>
+        <item x="625"/>
+        <item x="345"/>
+        <item x="280"/>
+        <item x="737"/>
+        <item x="888"/>
+        <item x="442"/>
+        <item x="290"/>
+        <item x="982"/>
+        <item x="177"/>
+        <item x="212"/>
+        <item x="242"/>
+        <item x="268"/>
+        <item x="28"/>
+        <item x="899"/>
+        <item x="983"/>
+        <item x="493"/>
+        <item x="725"/>
+        <item x="653"/>
+        <item x="630"/>
+        <item x="31"/>
+        <item x="344"/>
+        <item x="258"/>
+        <item x="911"/>
+        <item x="979"/>
+        <item x="862"/>
+        <item x="93"/>
+        <item x="596"/>
+        <item x="383"/>
+        <item x="264"/>
+        <item x="875"/>
+        <item x="641"/>
+        <item x="978"/>
+        <item x="759"/>
+        <item x="234"/>
+        <item x="854"/>
+        <item x="51"/>
+        <item x="707"/>
+        <item x="100"/>
+        <item x="873"/>
+        <item x="655"/>
+        <item x="965"/>
+        <item x="542"/>
+        <item x="688"/>
+        <item x="391"/>
+        <item x="315"/>
+        <item x="727"/>
+        <item x="560"/>
+        <item x="176"/>
+        <item x="701"/>
+        <item x="865"/>
+        <item x="921"/>
+        <item x="311"/>
+        <item x="696"/>
+        <item x="379"/>
+        <item x="634"/>
+        <item x="712"/>
+        <item x="34"/>
+        <item x="417"/>
+        <item x="821"/>
+        <item x="908"/>
+        <item x="705"/>
+        <item x="454"/>
+        <item x="635"/>
+        <item x="127"/>
+        <item x="27"/>
+        <item x="984"/>
+        <item x="513"/>
+        <item x="809"/>
+        <item x="101"/>
+        <item x="667"/>
+        <item x="819"/>
+        <item x="130"/>
+        <item x="702"/>
+        <item x="443"/>
+        <item x="967"/>
+        <item x="693"/>
+        <item x="738"/>
+        <item x="556"/>
+        <item x="425"/>
+        <item x="63"/>
+        <item x="774"/>
+        <item x="954"/>
+        <item x="772"/>
+        <item x="370"/>
+        <item x="579"/>
+        <item x="511"/>
+        <item x="750"/>
+        <item x="552"/>
+        <item x="111"/>
+        <item x="728"/>
+        <item x="295"/>
+        <item x="236"/>
+        <item x="103"/>
+        <item x="549"/>
+        <item x="224"/>
+        <item x="153"/>
+        <item x="969"/>
+        <item x="243"/>
+        <item x="559"/>
+        <item x="122"/>
+        <item x="600"/>
+        <item x="518"/>
+        <item x="805"/>
+        <item x="976"/>
+        <item x="826"/>
+        <item x="91"/>
+        <item x="115"/>
+        <item x="1"/>
+        <item x="925"/>
+        <item x="287"/>
+        <item x="25"/>
+        <item x="314"/>
+        <item x="589"/>
+        <item x="112"/>
+        <item x="43"/>
+        <item x="68"/>
+        <item x="35"/>
+        <item x="469"/>
+        <item x="995"/>
+        <item x="461"/>
+        <item x="858"/>
+        <item x="166"/>
+        <item x="935"/>
+        <item x="446"/>
+        <item x="533"/>
+        <item x="402"/>
+        <item x="114"/>
+        <item x="830"/>
+        <item x="734"/>
+        <item x="149"/>
+        <item x="144"/>
+        <item x="220"/>
+        <item x="572"/>
+        <item x="568"/>
+        <item x="138"/>
+        <item x="685"/>
+        <item x="675"/>
+        <item x="54"/>
+        <item x="543"/>
+        <item x="932"/>
+        <item x="410"/>
+        <item x="481"/>
+        <item x="920"/>
+        <item x="730"/>
+        <item x="170"/>
+        <item x="758"/>
+        <item x="656"/>
+        <item x="13"/>
+        <item x="265"/>
+        <item x="369"/>
+        <item x="408"/>
+        <item x="960"/>
+        <item x="807"/>
+        <item x="436"/>
+        <item x="598"/>
+        <item x="715"/>
+        <item x="371"/>
+        <item x="148"/>
+        <item x="76"/>
+        <item x="793"/>
+        <item x="207"/>
+        <item x="691"/>
+        <item x="420"/>
+        <item x="988"/>
+        <item x="415"/>
+        <item x="713"/>
+        <item x="124"/>
+        <item x="233"/>
+        <item x="426"/>
+        <item x="839"/>
+        <item x="422"/>
+        <item x="364"/>
+        <item x="37"/>
+        <item x="22"/>
+        <item x="644"/>
+        <item x="677"/>
+        <item x="161"/>
+        <item x="325"/>
+        <item x="823"/>
+        <item x="611"/>
+        <item x="500"/>
+        <item x="586"/>
+        <item x="292"/>
+        <item x="223"/>
+        <item x="156"/>
+        <item x="141"/>
+        <item x="40"/>
+        <item x="503"/>
+        <item x="557"/>
+        <item x="288"/>
+        <item x="190"/>
+        <item x="613"/>
+        <item x="60"/>
+        <item x="306"/>
+        <item x="192"/>
+        <item x="526"/>
+        <item x="430"/>
+        <item x="74"/>
+        <item x="530"/>
+        <item x="754"/>
+        <item x="836"/>
+        <item x="380"/>
+        <item x="230"/>
+        <item x="253"/>
+        <item x="508"/>
+        <item x="116"/>
+        <item x="883"/>
+        <item x="841"/>
+        <item x="448"/>
+        <item x="729"/>
+        <item x="15"/>
+        <item x="20"/>
+        <item x="444"/>
+        <item x="423"/>
+        <item x="590"/>
+        <item x="996"/>
+        <item x="689"/>
+        <item x="186"/>
+        <item x="483"/>
+        <item x="951"/>
+        <item x="782"/>
+        <item x="298"/>
+        <item x="157"/>
+        <item x="629"/>
+        <item x="393"/>
+        <item x="538"/>
+        <item x="882"/>
+        <item x="910"/>
+        <item x="749"/>
+        <item x="7"/>
+        <item x="396"/>
+        <item x="171"/>
+        <item x="859"/>
+        <item x="293"/>
+        <item x="608"/>
+        <item x="89"/>
+        <item x="637"/>
+        <item x="19"/>
+        <item x="217"/>
+        <item x="463"/>
+        <item x="354"/>
+        <item x="681"/>
+        <item x="926"/>
+        <item x="660"/>
+        <item x="801"/>
+        <item x="961"/>
+        <item x="429"/>
+        <item x="886"/>
+        <item x="458"/>
+        <item x="462"/>
+        <item x="50"/>
+        <item x="616"/>
+        <item x="18"/>
+        <item x="944"/>
+        <item x="38"/>
+        <item x="599"/>
+        <item x="123"/>
+        <item x="142"/>
+        <item x="536"/>
+        <item x="582"/>
+        <item x="527"/>
+        <item x="575"/>
+        <item x="471"/>
+        <item x="329"/>
+        <item x="179"/>
+        <item x="571"/>
+        <item x="832"/>
+        <item x="541"/>
+        <item x="437"/>
+        <item x="744"/>
+        <item x="399"/>
+        <item x="238"/>
+        <item x="62"/>
+        <item x="998"/>
+        <item x="510"/>
+        <item x="609"/>
+        <item x="10"/>
+        <item x="42"/>
+        <item x="137"/>
+        <item x="573"/>
+        <item x="6"/>
+        <item x="555"/>
+        <item x="539"/>
+        <item x="583"/>
+        <item x="798"/>
+        <item x="84"/>
+        <item x="866"/>
+        <item x="937"/>
+        <item x="86"/>
+        <item x="638"/>
+        <item x="963"/>
+        <item x="949"/>
+        <item x="12"/>
+        <item x="820"/>
+        <item x="256"/>
+        <item x="650"/>
+        <item x="46"/>
+        <item x="682"/>
+        <item x="21"/>
+        <item x="409"/>
+        <item x="694"/>
+        <item x="322"/>
+        <item x="602"/>
+        <item x="742"/>
+        <item x="4"/>
+        <item x="948"/>
+        <item x="339"/>
+        <item x="985"/>
+        <item x="584"/>
+        <item x="244"/>
+        <item x="277"/>
+        <item x="900"/>
+        <item x="340"/>
+        <item x="119"/>
+        <item x="588"/>
+        <item x="811"/>
+        <item x="259"/>
+        <item x="77"/>
+        <item x="69"/>
+        <item x="373"/>
+        <item x="959"/>
+        <item x="736"/>
+        <item x="506"/>
+        <item x="767"/>
+        <item x="222"/>
+        <item x="890"/>
+        <item x="745"/>
+        <item x="580"/>
+        <item x="445"/>
+        <item x="70"/>
+        <item x="441"/>
+        <item x="388"/>
+        <item x="204"/>
+        <item x="690"/>
+        <item x="304"/>
+        <item x="927"/>
+        <item x="55"/>
+        <item x="553"/>
+        <item x="349"/>
+        <item x="188"/>
+        <item x="791"/>
+        <item x="154"/>
+        <item x="799"/>
+        <item x="498"/>
+        <item x="785"/>
+        <item x="472"/>
+        <item x="757"/>
+        <item x="178"/>
+        <item x="569"/>
+        <item x="668"/>
+        <item x="851"/>
+        <item x="897"/>
+        <item x="762"/>
+        <item x="305"/>
+        <item x="515"/>
+        <item x="174"/>
+        <item x="343"/>
+        <item x="829"/>
+        <item x="232"/>
+        <item x="720"/>
+        <item x="633"/>
+        <item x="199"/>
+        <item x="499"/>
+        <item x="620"/>
+        <item x="610"/>
+        <item x="374"/>
+        <item x="159"/>
+        <item x="313"/>
+        <item x="163"/>
+        <item x="516"/>
+        <item x="202"/>
+        <item x="834"/>
+        <item x="316"/>
+        <item x="957"/>
+        <item x="989"/>
+        <item x="289"/>
+        <item x="928"/>
+        <item x="936"/>
+        <item x="341"/>
+        <item x="724"/>
+        <item x="181"/>
+        <item x="531"/>
+        <item x="621"/>
+        <item x="494"/>
+        <item x="191"/>
+        <item x="485"/>
+        <item x="733"/>
+        <item x="303"/>
+        <item x="466"/>
+        <item x="346"/>
+        <item x="726"/>
+        <item x="333"/>
+        <item x="614"/>
+        <item x="796"/>
+        <item x="581"/>
+        <item x="709"/>
+        <item x="300"/>
+        <item x="263"/>
+        <item x="971"/>
+        <item x="878"/>
+        <item x="241"/>
+        <item x="943"/>
+        <item x="449"/>
+        <item x="440"/>
+        <item x="906"/>
+        <item x="521"/>
+        <item x="741"/>
+        <item x="972"/>
+        <item x="447"/>
+        <item x="912"/>
+        <item x="358"/>
+        <item x="924"/>
+        <item x="746"/>
+        <item x="779"/>
+        <item x="933"/>
+        <item x="145"/>
+        <item x="576"/>
+        <item x="914"/>
+        <item x="432"/>
+        <item x="540"/>
+        <item x="885"/>
+        <item x="363"/>
+        <item x="381"/>
+        <item x="228"/>
+        <item x="221"/>
+        <item x="367"/>
+        <item x="783"/>
+        <item x="595"/>
+        <item x="464"/>
+        <item x="773"/>
+        <item x="362"/>
+        <item x="414"/>
+        <item x="802"/>
+        <item x="274"/>
+        <item x="816"/>
+        <item x="239"/>
+        <item x="110"/>
+        <item x="82"/>
+        <item x="717"/>
+        <item x="134"/>
+        <item x="604"/>
+        <item x="476"/>
+        <item x="748"/>
+        <item x="143"/>
+        <item x="424"/>
+        <item x="945"/>
+        <item x="282"/>
+        <item x="880"/>
+        <item x="659"/>
+        <item x="484"/>
+        <item x="840"/>
+        <item x="789"/>
+        <item x="285"/>
+        <item x="815"/>
+        <item x="939"/>
+        <item x="934"/>
+        <item x="475"/>
+        <item x="514"/>
+        <item x="950"/>
+        <item x="88"/>
+        <item x="165"/>
+        <item x="901"/>
+        <item x="615"/>
+        <item x="491"/>
+        <item x="684"/>
+        <item x="72"/>
+        <item x="504"/>
+        <item x="94"/>
+        <item x="308"/>
+        <item x="564"/>
+        <item x="784"/>
+        <item x="665"/>
+        <item x="977"/>
+        <item x="517"/>
+        <item x="913"/>
+        <item x="281"/>
+        <item x="761"/>
+        <item x="385"/>
+        <item x="276"/>
+        <item x="335"/>
+        <item x="833"/>
+        <item x="680"/>
+        <item x="11"/>
+        <item x="245"/>
+        <item x="973"/>
+        <item x="348"/>
+        <item x="310"/>
+        <item x="457"/>
+        <item x="863"/>
+        <item x="524"/>
+        <item x="781"/>
+        <item x="278"/>
+        <item x="828"/>
+        <item x="548"/>
+        <item x="240"/>
+        <item x="480"/>
+        <item x="547"/>
+        <item x="390"/>
+        <item x="201"/>
+        <item x="607"/>
+        <item x="872"/>
+        <item x="904"/>
+        <item x="231"/>
+        <item x="743"/>
+        <item x="164"/>
+        <item x="884"/>
+        <item x="218"/>
+        <item x="843"/>
+        <item x="24"/>
+        <item x="129"/>
+        <item x="438"/>
+        <item x="574"/>
+        <item x="102"/>
+        <item x="987"/>
+        <item x="357"/>
+        <item x="467"/>
+        <item x="41"/>
+        <item x="673"/>
+        <item x="488"/>
+        <item x="195"/>
+        <item x="496"/>
+        <item x="966"/>
+        <item x="291"/>
+        <item x="808"/>
+        <item x="606"/>
+        <item x="216"/>
+        <item x="592"/>
+        <item x="657"/>
+        <item x="392"/>
+        <item x="651"/>
+        <item x="323"/>
+        <item x="284"/>
+        <item x="353"/>
+        <item x="90"/>
+        <item x="810"/>
+        <item x="275"/>
+        <item x="332"/>
+        <item x="453"/>
+        <item x="147"/>
+        <item x="411"/>
+        <item x="825"/>
+        <item x="267"/>
+        <item x="301"/>
+        <item x="208"/>
+        <item x="501"/>
+        <item x="49"/>
+        <item x="647"/>
+        <item x="431"/>
+        <item x="952"/>
+        <item x="139"/>
+        <item x="479"/>
+        <item x="672"/>
+        <item x="956"/>
+        <item x="359"/>
+        <item x="551"/>
+        <item x="535"/>
+        <item x="227"/>
+        <item x="871"/>
+        <item x="151"/>
+        <item x="294"/>
+        <item x="594"/>
+        <item x="751"/>
+        <item x="846"/>
+        <item x="184"/>
+        <item x="404"/>
+        <item x="763"/>
+        <item x="108"/>
+        <item x="670"/>
+        <item x="632"/>
+        <item x="133"/>
+        <item x="577"/>
+        <item x="723"/>
+        <item x="962"/>
+        <item x="765"/>
+        <item x="189"/>
+        <item x="286"/>
+        <item x="95"/>
+        <item x="33"/>
+        <item x="512"/>
+        <item x="378"/>
+        <item x="902"/>
+        <item x="389"/>
+        <item x="135"/>
+        <item x="624"/>
+        <item x="477"/>
+        <item x="519"/>
+        <item x="991"/>
+        <item x="509"/>
+        <item x="317"/>
+        <item x="247"/>
+        <item x="968"/>
+        <item x="361"/>
+        <item x="795"/>
+        <item x="200"/>
+        <item x="735"/>
+        <item x="892"/>
+        <item x="492"/>
+        <item x="877"/>
+        <item x="173"/>
+        <item x="150"/>
+        <item x="522"/>
+        <item x="636"/>
+        <item x="360"/>
+        <item x="368"/>
+        <item x="52"/>
+        <item x="433"/>
+        <item x="44"/>
+        <item x="806"/>
+        <item x="502"/>
+        <item x="321"/>
+        <item x="909"/>
+        <item x="700"/>
+        <item x="489"/>
+        <item x="106"/>
+        <item x="627"/>
+        <item x="780"/>
+        <item x="107"/>
+        <item x="868"/>
+        <item x="2"/>
+        <item x="495"/>
+        <item x="356"/>
+        <item x="338"/>
+        <item x="87"/>
+        <item x="273"/>
+        <item x="331"/>
+        <item x="731"/>
+        <item x="57"/>
+        <item x="831"/>
+        <item x="23"/>
+        <item x="919"/>
+        <item x="120"/>
+        <item x="460"/>
+        <item x="704"/>
+        <item x="32"/>
+        <item x="193"/>
+        <item x="663"/>
+        <item x="930"/>
+        <item x="619"/>
+        <item x="603"/>
+        <item x="118"/>
+        <item x="671"/>
+        <item x="537"/>
+        <item x="113"/>
+        <item x="235"/>
+        <item x="546"/>
+        <item x="687"/>
+        <item x="678"/>
+        <item x="320"/>
+        <item x="26"/>
+        <item x="427"/>
+        <item x="401"/>
+        <item x="567"/>
+        <item x="790"/>
+        <item x="755"/>
+        <item x="994"/>
+        <item x="631"/>
+        <item x="262"/>
+        <item x="213"/>
+        <item x="16"/>
+        <item x="852"/>
+        <item x="121"/>
+        <item x="117"/>
+        <item x="838"/>
+        <item x="251"/>
+        <item x="384"/>
+        <item x="128"/>
+        <item x="747"/>
+        <item x="8"/>
+        <item x="639"/>
+        <item x="375"/>
+        <item x="283"/>
+        <item x="125"/>
+        <item x="48"/>
+        <item x="837"/>
+        <item x="622"/>
+        <item x="206"/>
+        <item x="482"/>
+        <item x="813"/>
+        <item x="947"/>
+        <item x="474"/>
+        <item x="211"/>
+        <item x="721"/>
+        <item x="669"/>
+        <item x="146"/>
+        <item x="490"/>
+        <item x="271"/>
+        <item x="167"/>
+        <item x="692"/>
+        <item x="386"/>
+        <item x="993"/>
+        <item x="337"/>
+        <item x="9"/>
+        <item x="640"/>
+        <item x="587"/>
+        <item x="132"/>
+        <item x="413"/>
+        <item x="565"/>
+        <item x="198"/>
+        <item x="5"/>
+        <item x="895"/>
+        <item x="136"/>
+        <item x="545"/>
+        <item x="478"/>
+        <item x="794"/>
+        <item x="941"/>
+        <item x="788"/>
+        <item x="254"/>
+        <item x="318"/>
+        <item x="105"/>
+        <item x="645"/>
+        <item x="770"/>
+        <item x="486"/>
+        <item x="456"/>
+        <item x="768"/>
+        <item x="558"/>
+        <item x="664"/>
+        <item x="893"/>
+        <item x="104"/>
+        <item x="915"/>
+        <item x="566"/>
+        <item x="327"/>
+        <item x="525"/>
+        <item x="940"/>
+        <item x="229"/>
+        <item x="916"/>
+        <item x="407"/>
+        <item x="898"/>
+        <item x="387"/>
+        <item x="662"/>
+        <item x="347"/>
+        <item x="395"/>
+        <item x="505"/>
+        <item x="997"/>
+        <item x="452"/>
+        <item x="47"/>
+        <item x="296"/>
+        <item x="980"/>
+        <item x="711"/>
+        <item x="703"/>
+        <item x="257"/>
+        <item x="459"/>
+        <item x="85"/>
+        <item x="328"/>
+        <item x="372"/>
+        <item x="269"/>
+        <item x="473"/>
+        <item x="140"/>
+        <item x="187"/>
+        <item x="406"/>
+        <item x="75"/>
+        <item x="99"/>
+        <item x="740"/>
+        <item x="172"/>
+        <item x="520"/>
+        <item x="302"/>
+        <item x="714"/>
+        <item x="874"/>
+        <item x="649"/>
+        <item x="421"/>
+        <item x="428"/>
+        <item x="652"/>
+        <item x="158"/>
+        <item x="377"/>
+        <item x="297"/>
+        <item x="451"/>
+        <item x="792"/>
+        <item x="974"/>
+        <item x="419"/>
+        <item x="992"/>
+        <item x="970"/>
+        <item x="468"/>
+        <item x="324"/>
+        <item x="225"/>
+        <item x="152"/>
+        <item x="550"/>
+        <item x="857"/>
+        <item x="205"/>
+        <item x="917"/>
+        <item x="416"/>
+        <item x="0"/>
+        <item x="800"/>
+        <item x="699"/>
+        <item x="435"/>
+        <item x="676"/>
+        <item x="237"/>
+        <item x="79"/>
+        <item x="732"/>
+        <item x="931"/>
+        <item x="803"/>
+        <item x="771"/>
+        <item x="708"/>
+        <item x="827"/>
+        <item x="397"/>
+        <item x="563"/>
+        <item x="879"/>
+        <item x="986"/>
+        <item x="17"/>
+        <item x="96"/>
+        <item x="470"/>
+        <item x="455"/>
+        <item x="686"/>
+        <item x="856"/>
+        <item x="753"/>
+        <item x="722"/>
+        <item x="918"/>
+        <item x="39"/>
+        <item x="814"/>
+        <item x="53"/>
+        <item x="646"/>
+        <item x="299"/>
+        <item x="666"/>
+        <item x="896"/>
+        <item x="155"/>
+        <item x="270"/>
+        <item x="953"/>
+        <item x="822"/>
+        <item x="249"/>
+        <item x="756"/>
+        <item x="710"/>
+        <item x="319"/>
+        <item x="83"/>
+        <item x="764"/>
+        <item x="591"/>
+        <item x="718"/>
+        <item x="612"/>
+        <item x="219"/>
+        <item x="787"/>
+        <item x="398"/>
+        <item x="642"/>
+        <item x="964"/>
+        <item x="487"/>
+        <item x="71"/>
+        <item x="168"/>
+        <item x="578"/>
+        <item x="248"/>
+        <item x="695"/>
+        <item x="766"/>
+        <item x="215"/>
+        <item x="131"/>
+        <item x="307"/>
+        <item x="61"/>
+        <item x="845"/>
+        <item x="739"/>
+        <item x="752"/>
+        <item x="835"/>
+        <item x="266"/>
+        <item x="981"/>
+        <item x="942"/>
+        <item x="439"/>
+        <item x="674"/>
+        <item x="894"/>
+        <item x="812"/>
+        <item x="326"/>
+        <item x="626"/>
+        <item x="658"/>
+        <item x="58"/>
+        <item x="209"/>
+        <item x="261"/>
+        <item x="719"/>
+        <item x="183"/>
+        <item x="929"/>
+        <item x="697"/>
+        <item x="175"/>
+        <item x="528"/>
+        <item x="529"/>
+        <item x="618"/>
+        <item x="279"/>
+        <item x="14"/>
+        <item x="78"/>
+        <item x="605"/>
+        <item x="194"/>
+        <item x="403"/>
+        <item x="804"/>
+        <item x="817"/>
+        <item x="365"/>
+        <item x="706"/>
+        <item x="351"/>
+        <item x="570"/>
+        <item x="334"/>
+        <item x="226"/>
+        <item x="434"/>
+        <item x="922"/>
+        <item x="66"/>
+        <item x="617"/>
+        <item x="861"/>
+        <item x="544"/>
+        <item x="73"/>
+        <item x="661"/>
+        <item x="760"/>
+        <item x="376"/>
+        <item x="850"/>
+        <item x="250"/>
+        <item x="848"/>
+        <item x="955"/>
+        <item x="81"/>
+        <item x="418"/>
+        <item x="196"/>
+        <item x="309"/>
+        <item x="29"/>
+        <item x="860"/>
+        <item x="999"/>
+        <item x="260"/>
+        <item x="182"/>
+        <item x="907"/>
+        <item x="623"/>
+        <item x="869"/>
+        <item x="64"/>
+        <item x="197"/>
+        <item x="628"/>
+        <item x="716"/>
+        <item x="532"/>
+        <item x="648"/>
+        <item x="946"/>
+        <item x="842"/>
+        <item x="350"/>
+        <item x="109"/>
+        <item x="507"/>
+        <item x="847"/>
+        <item x="497"/>
+        <item x="797"/>
+        <item x="903"/>
+        <item x="98"/>
+        <item x="246"/>
+        <item x="853"/>
+        <item x="561"/>
+        <item x="958"/>
+        <item x="698"/>
+        <item x="382"/>
+        <item x="330"/>
+        <item x="818"/>
+        <item x="126"/>
+        <item x="80"/>
+        <item x="312"/>
+        <item x="97"/>
+        <item x="30"/>
+        <item x="870"/>
+        <item x="92"/>
+        <item x="342"/>
+        <item x="777"/>
+        <item x="203"/>
+        <item x="65"/>
+        <item x="465"/>
+        <item x="593"/>
+        <item x="889"/>
+        <item x="601"/>
+        <item x="405"/>
+        <item x="252"/>
+        <item x="975"/>
+        <item x="887"/>
+        <item x="394"/>
+        <item x="876"/>
+        <item x="990"/>
+        <item x="769"/>
+        <item x="786"/>
+        <item x="923"/>
+        <item x="210"/>
+        <item x="355"/>
+        <item x="450"/>
+        <item x="214"/>
+        <item x="534"/>
+        <item x="160"/>
+        <item x="855"/>
+        <item x="185"/>
+        <item x="844"/>
+        <item x="336"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="1"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="90">
+        <item x="17"/>
+        <item x="56"/>
+        <item x="75"/>
+        <item x="72"/>
+        <item x="0"/>
+        <item x="47"/>
+        <item x="27"/>
+        <item x="66"/>
+        <item x="51"/>
+        <item x="8"/>
+        <item x="83"/>
+        <item x="52"/>
+        <item x="50"/>
+        <item x="78"/>
+        <item x="15"/>
+        <item x="65"/>
+        <item x="29"/>
+        <item x="68"/>
+        <item x="64"/>
+        <item x="40"/>
+        <item x="18"/>
+        <item x="49"/>
+        <item x="54"/>
+        <item x="46"/>
+        <item x="25"/>
+        <item x="53"/>
+        <item x="3"/>
+        <item x="26"/>
+        <item x="71"/>
+        <item x="74"/>
+        <item x="82"/>
+        <item x="60"/>
+        <item x="30"/>
+        <item x="36"/>
+        <item x="87"/>
+        <item x="63"/>
+        <item x="10"/>
+        <item x="13"/>
+        <item x="4"/>
+        <item x="57"/>
+        <item x="34"/>
+        <item x="48"/>
+        <item x="12"/>
+        <item x="77"/>
+        <item x="44"/>
+        <item x="42"/>
+        <item x="69"/>
+        <item x="21"/>
+        <item x="67"/>
+        <item x="88"/>
+        <item x="9"/>
+        <item x="81"/>
+        <item x="70"/>
+        <item x="55"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="84"/>
+        <item x="33"/>
+        <item x="38"/>
+        <item x="59"/>
+        <item x="22"/>
+        <item x="2"/>
+        <item x="31"/>
+        <item x="19"/>
+        <item x="43"/>
+        <item x="37"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="24"/>
+        <item x="16"/>
+        <item x="41"/>
+        <item x="45"/>
+        <item x="86"/>
+        <item x="20"/>
+        <item x="32"/>
+        <item x="85"/>
+        <item x="79"/>
+        <item x="35"/>
+        <item x="80"/>
+        <item x="76"/>
+        <item x="23"/>
+        <item x="28"/>
+        <item x="62"/>
+        <item x="5"/>
+        <item x="58"/>
+        <item x="39"/>
+        <item x="61"/>
+        <item x="14"/>
+        <item x="73"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="20" showAll="0"/>
+    <pivotField showAll="0" countASubtotal="1">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="countA"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" sortType="descending">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="105">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{81DC4A31-0BDF-4AA7-888F-6BFE593127CD}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="G8:H12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField showAll="0">
+      <items count="1001">
+        <item x="162"/>
+        <item x="867"/>
+        <item x="778"/>
+        <item x="776"/>
+        <item x="683"/>
+        <item x="169"/>
+        <item x="56"/>
+        <item x="67"/>
+        <item x="824"/>
+        <item x="400"/>
+        <item x="255"/>
+        <item x="891"/>
+        <item x="881"/>
+        <item x="352"/>
+        <item x="905"/>
+        <item x="59"/>
+        <item x="775"/>
+        <item x="366"/>
+        <item x="3"/>
+        <item x="597"/>
+        <item x="864"/>
+        <item x="849"/>
+        <item x="272"/>
+        <item x="585"/>
+        <item x="36"/>
+        <item x="679"/>
+        <item x="180"/>
+        <item x="643"/>
+        <item x="938"/>
+        <item x="412"/>
+        <item x="45"/>
+        <item x="523"/>
+        <item x="654"/>
+        <item x="562"/>
+        <item x="554"/>
+        <item x="625"/>
+        <item x="345"/>
+        <item x="280"/>
+        <item x="737"/>
+        <item x="888"/>
+        <item x="442"/>
+        <item x="290"/>
+        <item x="982"/>
+        <item x="177"/>
+        <item x="212"/>
+        <item x="242"/>
+        <item x="268"/>
+        <item x="28"/>
+        <item x="899"/>
+        <item x="983"/>
+        <item x="493"/>
+        <item x="725"/>
+        <item x="653"/>
+        <item x="630"/>
+        <item x="31"/>
+        <item x="344"/>
+        <item x="258"/>
+        <item x="911"/>
+        <item x="979"/>
+        <item x="862"/>
+        <item x="93"/>
+        <item x="596"/>
+        <item x="383"/>
+        <item x="264"/>
+        <item x="875"/>
+        <item x="641"/>
+        <item x="978"/>
+        <item x="759"/>
+        <item x="234"/>
+        <item x="854"/>
+        <item x="51"/>
+        <item x="707"/>
+        <item x="100"/>
+        <item x="873"/>
+        <item x="655"/>
+        <item x="965"/>
+        <item x="542"/>
+        <item x="688"/>
+        <item x="391"/>
+        <item x="315"/>
+        <item x="727"/>
+        <item x="560"/>
+        <item x="176"/>
+        <item x="701"/>
+        <item x="865"/>
+        <item x="921"/>
+        <item x="311"/>
+        <item x="696"/>
+        <item x="379"/>
+        <item x="634"/>
+        <item x="712"/>
+        <item x="34"/>
+        <item x="417"/>
+        <item x="821"/>
+        <item x="908"/>
+        <item x="705"/>
+        <item x="454"/>
+        <item x="635"/>
+        <item x="127"/>
+        <item x="27"/>
+        <item x="984"/>
+        <item x="513"/>
+        <item x="809"/>
+        <item x="101"/>
+        <item x="667"/>
+        <item x="819"/>
+        <item x="130"/>
+        <item x="702"/>
+        <item x="443"/>
+        <item x="967"/>
+        <item x="693"/>
+        <item x="738"/>
+        <item x="556"/>
+        <item x="425"/>
+        <item x="63"/>
+        <item x="774"/>
+        <item x="954"/>
+        <item x="772"/>
+        <item x="370"/>
+        <item x="579"/>
+        <item x="511"/>
+        <item x="750"/>
+        <item x="552"/>
+        <item x="111"/>
+        <item x="728"/>
+        <item x="295"/>
+        <item x="236"/>
+        <item x="103"/>
+        <item x="549"/>
+        <item x="224"/>
+        <item x="153"/>
+        <item x="969"/>
+        <item x="243"/>
+        <item x="559"/>
+        <item x="122"/>
+        <item x="600"/>
+        <item x="518"/>
+        <item x="805"/>
+        <item x="976"/>
+        <item x="826"/>
+        <item x="91"/>
+        <item x="115"/>
+        <item x="1"/>
+        <item x="925"/>
+        <item x="287"/>
+        <item x="25"/>
+        <item x="314"/>
+        <item x="589"/>
+        <item x="112"/>
+        <item x="43"/>
+        <item x="68"/>
+        <item x="35"/>
+        <item x="469"/>
+        <item x="995"/>
+        <item x="461"/>
+        <item x="858"/>
+        <item x="166"/>
+        <item x="935"/>
+        <item x="446"/>
+        <item x="533"/>
+        <item x="402"/>
+        <item x="114"/>
+        <item x="830"/>
+        <item x="734"/>
+        <item x="149"/>
+        <item x="144"/>
+        <item x="220"/>
+        <item x="572"/>
+        <item x="568"/>
+        <item x="138"/>
+        <item x="685"/>
+        <item x="675"/>
+        <item x="54"/>
+        <item x="543"/>
+        <item x="932"/>
+        <item x="410"/>
+        <item x="481"/>
+        <item x="920"/>
+        <item x="730"/>
+        <item x="170"/>
+        <item x="758"/>
+        <item x="656"/>
+        <item x="13"/>
+        <item x="265"/>
+        <item x="369"/>
+        <item x="408"/>
+        <item x="960"/>
+        <item x="807"/>
+        <item x="436"/>
+        <item x="598"/>
+        <item x="715"/>
+        <item x="371"/>
+        <item x="148"/>
+        <item x="76"/>
+        <item x="793"/>
+        <item x="207"/>
+        <item x="691"/>
+        <item x="420"/>
+        <item x="988"/>
+        <item x="415"/>
+        <item x="713"/>
+        <item x="124"/>
+        <item x="233"/>
+        <item x="426"/>
+        <item x="839"/>
+        <item x="422"/>
+        <item x="364"/>
+        <item x="37"/>
+        <item x="22"/>
+        <item x="644"/>
+        <item x="677"/>
+        <item x="161"/>
+        <item x="325"/>
+        <item x="823"/>
+        <item x="611"/>
+        <item x="500"/>
+        <item x="586"/>
+        <item x="292"/>
+        <item x="223"/>
+        <item x="156"/>
+        <item x="141"/>
+        <item x="40"/>
+        <item x="503"/>
+        <item x="557"/>
+        <item x="288"/>
+        <item x="190"/>
+        <item x="613"/>
+        <item x="60"/>
+        <item x="306"/>
+        <item x="192"/>
+        <item x="526"/>
+        <item x="430"/>
+        <item x="74"/>
+        <item x="530"/>
+        <item x="754"/>
+        <item x="836"/>
+        <item x="380"/>
+        <item x="230"/>
+        <item x="253"/>
+        <item x="508"/>
+        <item x="116"/>
+        <item x="883"/>
+        <item x="841"/>
+        <item x="448"/>
+        <item x="729"/>
+        <item x="15"/>
+        <item x="20"/>
+        <item x="444"/>
+        <item x="423"/>
+        <item x="590"/>
+        <item x="996"/>
+        <item x="689"/>
+        <item x="186"/>
+        <item x="483"/>
+        <item x="951"/>
+        <item x="782"/>
+        <item x="298"/>
+        <item x="157"/>
+        <item x="629"/>
+        <item x="393"/>
+        <item x="538"/>
+        <item x="882"/>
+        <item x="910"/>
+        <item x="749"/>
+        <item x="7"/>
+        <item x="396"/>
+        <item x="171"/>
+        <item x="859"/>
+        <item x="293"/>
+        <item x="608"/>
+        <item x="89"/>
+        <item x="637"/>
+        <item x="19"/>
+        <item x="217"/>
+        <item x="463"/>
+        <item x="354"/>
+        <item x="681"/>
+        <item x="926"/>
+        <item x="660"/>
+        <item x="801"/>
+        <item x="961"/>
+        <item x="429"/>
+        <item x="886"/>
+        <item x="458"/>
+        <item x="462"/>
+        <item x="50"/>
+        <item x="616"/>
+        <item x="18"/>
+        <item x="944"/>
+        <item x="38"/>
+        <item x="599"/>
+        <item x="123"/>
+        <item x="142"/>
+        <item x="536"/>
+        <item x="582"/>
+        <item x="527"/>
+        <item x="575"/>
+        <item x="471"/>
+        <item x="329"/>
+        <item x="179"/>
+        <item x="571"/>
+        <item x="832"/>
+        <item x="541"/>
+        <item x="437"/>
+        <item x="744"/>
+        <item x="399"/>
+        <item x="238"/>
+        <item x="62"/>
+        <item x="998"/>
+        <item x="510"/>
+        <item x="609"/>
+        <item x="10"/>
+        <item x="42"/>
+        <item x="137"/>
+        <item x="573"/>
+        <item x="6"/>
+        <item x="555"/>
+        <item x="539"/>
+        <item x="583"/>
+        <item x="798"/>
+        <item x="84"/>
+        <item x="866"/>
+        <item x="937"/>
+        <item x="86"/>
+        <item x="638"/>
+        <item x="963"/>
+        <item x="949"/>
+        <item x="12"/>
+        <item x="820"/>
+        <item x="256"/>
+        <item x="650"/>
+        <item x="46"/>
+        <item x="682"/>
+        <item x="21"/>
+        <item x="409"/>
+        <item x="694"/>
+        <item x="322"/>
+        <item x="602"/>
+        <item x="742"/>
+        <item x="4"/>
+        <item x="948"/>
+        <item x="339"/>
+        <item x="985"/>
+        <item x="584"/>
+        <item x="244"/>
+        <item x="277"/>
+        <item x="900"/>
+        <item x="340"/>
+        <item x="119"/>
+        <item x="588"/>
+        <item x="811"/>
+        <item x="259"/>
+        <item x="77"/>
+        <item x="69"/>
+        <item x="373"/>
+        <item x="959"/>
+        <item x="736"/>
+        <item x="506"/>
+        <item x="767"/>
+        <item x="222"/>
+        <item x="890"/>
+        <item x="745"/>
+        <item x="580"/>
+        <item x="445"/>
+        <item x="70"/>
+        <item x="441"/>
+        <item x="388"/>
+        <item x="204"/>
+        <item x="690"/>
+        <item x="304"/>
+        <item x="927"/>
+        <item x="55"/>
+        <item x="553"/>
+        <item x="349"/>
+        <item x="188"/>
+        <item x="791"/>
+        <item x="154"/>
+        <item x="799"/>
+        <item x="498"/>
+        <item x="785"/>
+        <item x="472"/>
+        <item x="757"/>
+        <item x="178"/>
+        <item x="569"/>
+        <item x="668"/>
+        <item x="851"/>
+        <item x="897"/>
+        <item x="762"/>
+        <item x="305"/>
+        <item x="515"/>
+        <item x="174"/>
+        <item x="343"/>
+        <item x="829"/>
+        <item x="232"/>
+        <item x="720"/>
+        <item x="633"/>
+        <item x="199"/>
+        <item x="499"/>
+        <item x="620"/>
+        <item x="610"/>
+        <item x="374"/>
+        <item x="159"/>
+        <item x="313"/>
+        <item x="163"/>
+        <item x="516"/>
+        <item x="202"/>
+        <item x="834"/>
+        <item x="316"/>
+        <item x="957"/>
+        <item x="989"/>
+        <item x="289"/>
+        <item x="928"/>
+        <item x="936"/>
+        <item x="341"/>
+        <item x="724"/>
+        <item x="181"/>
+        <item x="531"/>
+        <item x="621"/>
+        <item x="494"/>
+        <item x="191"/>
+        <item x="485"/>
+        <item x="733"/>
+        <item x="303"/>
+        <item x="466"/>
+        <item x="346"/>
+        <item x="726"/>
+        <item x="333"/>
+        <item x="614"/>
+        <item x="796"/>
+        <item x="581"/>
+        <item x="709"/>
+        <item x="300"/>
+        <item x="263"/>
+        <item x="971"/>
+        <item x="878"/>
+        <item x="241"/>
+        <item x="943"/>
+        <item x="449"/>
+        <item x="440"/>
+        <item x="906"/>
+        <item x="521"/>
+        <item x="741"/>
+        <item x="972"/>
+        <item x="447"/>
+        <item x="912"/>
+        <item x="358"/>
+        <item x="924"/>
+        <item x="746"/>
+        <item x="779"/>
+        <item x="933"/>
+        <item x="145"/>
+        <item x="576"/>
+        <item x="914"/>
+        <item x="432"/>
+        <item x="540"/>
+        <item x="885"/>
+        <item x="363"/>
+        <item x="381"/>
+        <item x="228"/>
+        <item x="221"/>
+        <item x="367"/>
+        <item x="783"/>
+        <item x="595"/>
+        <item x="464"/>
+        <item x="773"/>
+        <item x="362"/>
+        <item x="414"/>
+        <item x="802"/>
+        <item x="274"/>
+        <item x="816"/>
+        <item x="239"/>
+        <item x="110"/>
+        <item x="82"/>
+        <item x="717"/>
+        <item x="134"/>
+        <item x="604"/>
+        <item x="476"/>
+        <item x="748"/>
+        <item x="143"/>
+        <item x="424"/>
+        <item x="945"/>
+        <item x="282"/>
+        <item x="880"/>
+        <item x="659"/>
+        <item x="484"/>
+        <item x="840"/>
+        <item x="789"/>
+        <item x="285"/>
+        <item x="815"/>
+        <item x="939"/>
+        <item x="934"/>
+        <item x="475"/>
+        <item x="514"/>
+        <item x="950"/>
+        <item x="88"/>
+        <item x="165"/>
+        <item x="901"/>
+        <item x="615"/>
+        <item x="491"/>
+        <item x="684"/>
+        <item x="72"/>
+        <item x="504"/>
+        <item x="94"/>
+        <item x="308"/>
+        <item x="564"/>
+        <item x="784"/>
+        <item x="665"/>
+        <item x="977"/>
+        <item x="517"/>
+        <item x="913"/>
+        <item x="281"/>
+        <item x="761"/>
+        <item x="385"/>
+        <item x="276"/>
+        <item x="335"/>
+        <item x="833"/>
+        <item x="680"/>
+        <item x="11"/>
+        <item x="245"/>
+        <item x="973"/>
+        <item x="348"/>
+        <item x="310"/>
+        <item x="457"/>
+        <item x="863"/>
+        <item x="524"/>
+        <item x="781"/>
+        <item x="278"/>
+        <item x="828"/>
+        <item x="548"/>
+        <item x="240"/>
+        <item x="480"/>
+        <item x="547"/>
+        <item x="390"/>
+        <item x="201"/>
+        <item x="607"/>
+        <item x="872"/>
+        <item x="904"/>
+        <item x="231"/>
+        <item x="743"/>
+        <item x="164"/>
+        <item x="884"/>
+        <item x="218"/>
+        <item x="843"/>
+        <item x="24"/>
+        <item x="129"/>
+        <item x="438"/>
+        <item x="574"/>
+        <item x="102"/>
+        <item x="987"/>
+        <item x="357"/>
+        <item x="467"/>
+        <item x="41"/>
+        <item x="673"/>
+        <item x="488"/>
+        <item x="195"/>
+        <item x="496"/>
+        <item x="966"/>
+        <item x="291"/>
+        <item x="808"/>
+        <item x="606"/>
+        <item x="216"/>
+        <item x="592"/>
+        <item x="657"/>
+        <item x="392"/>
+        <item x="651"/>
+        <item x="323"/>
+        <item x="284"/>
+        <item x="353"/>
+        <item x="90"/>
+        <item x="810"/>
+        <item x="275"/>
+        <item x="332"/>
+        <item x="453"/>
+        <item x="147"/>
+        <item x="411"/>
+        <item x="825"/>
+        <item x="267"/>
+        <item x="301"/>
+        <item x="208"/>
+        <item x="501"/>
+        <item x="49"/>
+        <item x="647"/>
+        <item x="431"/>
+        <item x="952"/>
+        <item x="139"/>
+        <item x="479"/>
+        <item x="672"/>
+        <item x="956"/>
+        <item x="359"/>
+        <item x="551"/>
+        <item x="535"/>
+        <item x="227"/>
+        <item x="871"/>
+        <item x="151"/>
+        <item x="294"/>
+        <item x="594"/>
+        <item x="751"/>
+        <item x="846"/>
+        <item x="184"/>
+        <item x="404"/>
+        <item x="763"/>
+        <item x="108"/>
+        <item x="670"/>
+        <item x="632"/>
+        <item x="133"/>
+        <item x="577"/>
+        <item x="723"/>
+        <item x="962"/>
+        <item x="765"/>
+        <item x="189"/>
+        <item x="286"/>
+        <item x="95"/>
+        <item x="33"/>
+        <item x="512"/>
+        <item x="378"/>
+        <item x="902"/>
+        <item x="389"/>
+        <item x="135"/>
+        <item x="624"/>
+        <item x="477"/>
+        <item x="519"/>
+        <item x="991"/>
+        <item x="509"/>
+        <item x="317"/>
+        <item x="247"/>
+        <item x="968"/>
+        <item x="361"/>
+        <item x="795"/>
+        <item x="200"/>
+        <item x="735"/>
+        <item x="892"/>
+        <item x="492"/>
+        <item x="877"/>
+        <item x="173"/>
+        <item x="150"/>
+        <item x="522"/>
+        <item x="636"/>
+        <item x="360"/>
+        <item x="368"/>
+        <item x="52"/>
+        <item x="433"/>
+        <item x="44"/>
+        <item x="806"/>
+        <item x="502"/>
+        <item x="321"/>
+        <item x="909"/>
+        <item x="700"/>
+        <item x="489"/>
+        <item x="106"/>
+        <item x="627"/>
+        <item x="780"/>
+        <item x="107"/>
+        <item x="868"/>
+        <item x="2"/>
+        <item x="495"/>
+        <item x="356"/>
+        <item x="338"/>
+        <item x="87"/>
+        <item x="273"/>
+        <item x="331"/>
+        <item x="731"/>
+        <item x="57"/>
+        <item x="831"/>
+        <item x="23"/>
+        <item x="919"/>
+        <item x="120"/>
+        <item x="460"/>
+        <item x="704"/>
+        <item x="32"/>
+        <item x="193"/>
+        <item x="663"/>
+        <item x="930"/>
+        <item x="619"/>
+        <item x="603"/>
+        <item x="118"/>
+        <item x="671"/>
+        <item x="537"/>
+        <item x="113"/>
+        <item x="235"/>
+        <item x="546"/>
+        <item x="687"/>
+        <item x="678"/>
+        <item x="320"/>
+        <item x="26"/>
+        <item x="427"/>
+        <item x="401"/>
+        <item x="567"/>
+        <item x="790"/>
+        <item x="755"/>
+        <item x="994"/>
+        <item x="631"/>
+        <item x="262"/>
+        <item x="213"/>
+        <item x="16"/>
+        <item x="852"/>
+        <item x="121"/>
+        <item x="117"/>
+        <item x="838"/>
+        <item x="251"/>
+        <item x="384"/>
+        <item x="128"/>
+        <item x="747"/>
+        <item x="8"/>
+        <item x="639"/>
+        <item x="375"/>
+        <item x="283"/>
+        <item x="125"/>
+        <item x="48"/>
+        <item x="837"/>
+        <item x="622"/>
+        <item x="206"/>
+        <item x="482"/>
+        <item x="813"/>
+        <item x="947"/>
+        <item x="474"/>
+        <item x="211"/>
+        <item x="721"/>
+        <item x="669"/>
+        <item x="146"/>
+        <item x="490"/>
+        <item x="271"/>
+        <item x="167"/>
+        <item x="692"/>
+        <item x="386"/>
+        <item x="993"/>
+        <item x="337"/>
+        <item x="9"/>
+        <item x="640"/>
+        <item x="587"/>
+        <item x="132"/>
+        <item x="413"/>
+        <item x="565"/>
+        <item x="198"/>
+        <item x="5"/>
+        <item x="895"/>
+        <item x="136"/>
+        <item x="545"/>
+        <item x="478"/>
+        <item x="794"/>
+        <item x="941"/>
+        <item x="788"/>
+        <item x="254"/>
+        <item x="318"/>
+        <item x="105"/>
+        <item x="645"/>
+        <item x="770"/>
+        <item x="486"/>
+        <item x="456"/>
+        <item x="768"/>
+        <item x="558"/>
+        <item x="664"/>
+        <item x="893"/>
+        <item x="104"/>
+        <item x="915"/>
+        <item x="566"/>
+        <item x="327"/>
+        <item x="525"/>
+        <item x="940"/>
+        <item x="229"/>
+        <item x="916"/>
+        <item x="407"/>
+        <item x="898"/>
+        <item x="387"/>
+        <item x="662"/>
+        <item x="347"/>
+        <item x="395"/>
+        <item x="505"/>
+        <item x="997"/>
+        <item x="452"/>
+        <item x="47"/>
+        <item x="296"/>
+        <item x="980"/>
+        <item x="711"/>
+        <item x="703"/>
+        <item x="257"/>
+        <item x="459"/>
+        <item x="85"/>
+        <item x="328"/>
+        <item x="372"/>
+        <item x="269"/>
+        <item x="473"/>
+        <item x="140"/>
+        <item x="187"/>
+        <item x="406"/>
+        <item x="75"/>
+        <item x="99"/>
+        <item x="740"/>
+        <item x="172"/>
+        <item x="520"/>
+        <item x="302"/>
+        <item x="714"/>
+        <item x="874"/>
+        <item x="649"/>
+        <item x="421"/>
+        <item x="428"/>
+        <item x="652"/>
+        <item x="158"/>
+        <item x="377"/>
+        <item x="297"/>
+        <item x="451"/>
+        <item x="792"/>
+        <item x="974"/>
+        <item x="419"/>
+        <item x="992"/>
+        <item x="970"/>
+        <item x="468"/>
+        <item x="324"/>
+        <item x="225"/>
+        <item x="152"/>
+        <item x="550"/>
+        <item x="857"/>
+        <item x="205"/>
+        <item x="917"/>
+        <item x="416"/>
+        <item x="0"/>
+        <item x="800"/>
+        <item x="699"/>
+        <item x="435"/>
+        <item x="676"/>
+        <item x="237"/>
+        <item x="79"/>
+        <item x="732"/>
+        <item x="931"/>
+        <item x="803"/>
+        <item x="771"/>
+        <item x="708"/>
+        <item x="827"/>
+        <item x="397"/>
+        <item x="563"/>
+        <item x="879"/>
+        <item x="986"/>
+        <item x="17"/>
+        <item x="96"/>
+        <item x="470"/>
+        <item x="455"/>
+        <item x="686"/>
+        <item x="856"/>
+        <item x="753"/>
+        <item x="722"/>
+        <item x="918"/>
+        <item x="39"/>
+        <item x="814"/>
+        <item x="53"/>
+        <item x="646"/>
+        <item x="299"/>
+        <item x="666"/>
+        <item x="896"/>
+        <item x="155"/>
+        <item x="270"/>
+        <item x="953"/>
+        <item x="822"/>
+        <item x="249"/>
+        <item x="756"/>
+        <item x="710"/>
+        <item x="319"/>
+        <item x="83"/>
+        <item x="764"/>
+        <item x="591"/>
+        <item x="718"/>
+        <item x="612"/>
+        <item x="219"/>
+        <item x="787"/>
+        <item x="398"/>
+        <item x="642"/>
+        <item x="964"/>
+        <item x="487"/>
+        <item x="71"/>
+        <item x="168"/>
+        <item x="578"/>
+        <item x="248"/>
+        <item x="695"/>
+        <item x="766"/>
+        <item x="215"/>
+        <item x="131"/>
+        <item x="307"/>
+        <item x="61"/>
+        <item x="845"/>
+        <item x="739"/>
+        <item x="752"/>
+        <item x="835"/>
+        <item x="266"/>
+        <item x="981"/>
+        <item x="942"/>
+        <item x="439"/>
+        <item x="674"/>
+        <item x="894"/>
+        <item x="812"/>
+        <item x="326"/>
+        <item x="626"/>
+        <item x="658"/>
+        <item x="58"/>
+        <item x="209"/>
+        <item x="261"/>
+        <item x="719"/>
+        <item x="183"/>
+        <item x="929"/>
+        <item x="697"/>
+        <item x="175"/>
+        <item x="528"/>
+        <item x="529"/>
+        <item x="618"/>
+        <item x="279"/>
+        <item x="14"/>
+        <item x="78"/>
+        <item x="605"/>
+        <item x="194"/>
+        <item x="403"/>
+        <item x="804"/>
+        <item x="817"/>
+        <item x="365"/>
+        <item x="706"/>
+        <item x="351"/>
+        <item x="570"/>
+        <item x="334"/>
+        <item x="226"/>
+        <item x="434"/>
+        <item x="922"/>
+        <item x="66"/>
+        <item x="617"/>
+        <item x="861"/>
+        <item x="544"/>
+        <item x="73"/>
+        <item x="661"/>
+        <item x="760"/>
+        <item x="376"/>
+        <item x="850"/>
+        <item x="250"/>
+        <item x="848"/>
+        <item x="955"/>
+        <item x="81"/>
+        <item x="418"/>
+        <item x="196"/>
+        <item x="309"/>
+        <item x="29"/>
+        <item x="860"/>
+        <item x="999"/>
+        <item x="260"/>
+        <item x="182"/>
+        <item x="907"/>
+        <item x="623"/>
+        <item x="869"/>
+        <item x="64"/>
+        <item x="197"/>
+        <item x="628"/>
+        <item x="716"/>
+        <item x="532"/>
+        <item x="648"/>
+        <item x="946"/>
+        <item x="842"/>
+        <item x="350"/>
+        <item x="109"/>
+        <item x="507"/>
+        <item x="847"/>
+        <item x="497"/>
+        <item x="797"/>
+        <item x="903"/>
+        <item x="98"/>
+        <item x="246"/>
+        <item x="853"/>
+        <item x="561"/>
+        <item x="958"/>
+        <item x="698"/>
+        <item x="382"/>
+        <item x="330"/>
+        <item x="818"/>
+        <item x="126"/>
+        <item x="80"/>
+        <item x="312"/>
+        <item x="97"/>
+        <item x="30"/>
+        <item x="870"/>
+        <item x="92"/>
+        <item x="342"/>
+        <item x="777"/>
+        <item x="203"/>
+        <item x="65"/>
+        <item x="465"/>
+        <item x="593"/>
+        <item x="889"/>
+        <item x="601"/>
+        <item x="405"/>
+        <item x="252"/>
+        <item x="975"/>
+        <item x="887"/>
+        <item x="394"/>
+        <item x="876"/>
+        <item x="990"/>
+        <item x="769"/>
+        <item x="786"/>
+        <item x="923"/>
+        <item x="210"/>
+        <item x="355"/>
+        <item x="450"/>
+        <item x="214"/>
+        <item x="534"/>
+        <item x="160"/>
+        <item x="855"/>
+        <item x="185"/>
+        <item x="844"/>
+        <item x="336"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="1"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="90">
+        <item x="17"/>
+        <item x="56"/>
+        <item x="75"/>
+        <item x="72"/>
+        <item x="0"/>
+        <item x="47"/>
+        <item x="27"/>
+        <item x="66"/>
+        <item x="51"/>
+        <item x="8"/>
+        <item x="83"/>
+        <item x="52"/>
+        <item x="50"/>
+        <item x="78"/>
+        <item x="15"/>
+        <item x="65"/>
+        <item x="29"/>
+        <item x="68"/>
+        <item x="64"/>
+        <item x="40"/>
+        <item x="18"/>
+        <item x="49"/>
+        <item x="54"/>
+        <item x="46"/>
+        <item x="25"/>
+        <item x="53"/>
+        <item x="3"/>
+        <item x="26"/>
+        <item x="71"/>
+        <item x="74"/>
+        <item x="82"/>
+        <item x="60"/>
+        <item x="30"/>
+        <item x="36"/>
+        <item x="87"/>
+        <item x="63"/>
+        <item x="10"/>
+        <item x="13"/>
+        <item x="4"/>
+        <item x="57"/>
+        <item x="34"/>
+        <item x="48"/>
+        <item x="12"/>
+        <item x="77"/>
+        <item x="44"/>
+        <item x="42"/>
+        <item x="69"/>
+        <item x="21"/>
+        <item x="67"/>
+        <item x="88"/>
+        <item x="9"/>
+        <item x="81"/>
+        <item x="70"/>
+        <item x="55"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="84"/>
+        <item x="33"/>
+        <item x="38"/>
+        <item x="59"/>
+        <item x="22"/>
+        <item x="2"/>
+        <item x="31"/>
+        <item x="19"/>
+        <item x="43"/>
+        <item x="37"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="24"/>
+        <item x="16"/>
+        <item x="41"/>
+        <item x="45"/>
+        <item x="86"/>
+        <item x="20"/>
+        <item x="32"/>
+        <item x="85"/>
+        <item x="79"/>
+        <item x="35"/>
+        <item x="80"/>
+        <item x="76"/>
+        <item x="23"/>
+        <item x="28"/>
+        <item x="62"/>
+        <item x="5"/>
+        <item x="58"/>
+        <item x="39"/>
+        <item x="61"/>
+        <item x="14"/>
+        <item x="73"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="20" showAll="0"/>
+    <pivotField showAll="0" countASubtotal="1">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="countA"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="15">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="15"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="106">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="15" count="3">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9258275B-D203-43F3-A683-AF205FA405F5}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A7:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
@@ -35223,8 +39195,8 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="4">
-        <item x="0"/>
-        <item x="2"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -36345,19 +40317,19 @@
   </rowFields>
   <rowItems count="7">
     <i>
-      <x v="3"/>
-    </i>
-    <i>
       <x v="4"/>
     </i>
     <i>
-      <x v="1"/>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i>
       <x/>
     </i>
     <i>
-      <x v="5"/>
+      <x v="1"/>
     </i>
     <i>
       <x v="2"/>
@@ -36395,2485 +40367,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B3E162D0-00BF-4097-8067-334C9A57E3BD}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="G16:H19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField showAll="0">
-      <items count="1001">
-        <item x="162"/>
-        <item x="867"/>
-        <item x="778"/>
-        <item x="776"/>
-        <item x="683"/>
-        <item x="169"/>
-        <item x="56"/>
-        <item x="67"/>
-        <item x="824"/>
-        <item x="400"/>
-        <item x="255"/>
-        <item x="891"/>
-        <item x="881"/>
-        <item x="352"/>
-        <item x="905"/>
-        <item x="59"/>
-        <item x="775"/>
-        <item x="366"/>
-        <item x="3"/>
-        <item x="597"/>
-        <item x="864"/>
-        <item x="849"/>
-        <item x="272"/>
-        <item x="585"/>
-        <item x="36"/>
-        <item x="679"/>
-        <item x="180"/>
-        <item x="643"/>
-        <item x="938"/>
-        <item x="412"/>
-        <item x="45"/>
-        <item x="523"/>
-        <item x="654"/>
-        <item x="562"/>
-        <item x="554"/>
-        <item x="625"/>
-        <item x="345"/>
-        <item x="280"/>
-        <item x="737"/>
-        <item x="888"/>
-        <item x="442"/>
-        <item x="290"/>
-        <item x="982"/>
-        <item x="177"/>
-        <item x="212"/>
-        <item x="242"/>
-        <item x="268"/>
-        <item x="28"/>
-        <item x="899"/>
-        <item x="983"/>
-        <item x="493"/>
-        <item x="725"/>
-        <item x="653"/>
-        <item x="630"/>
-        <item x="31"/>
-        <item x="344"/>
-        <item x="258"/>
-        <item x="911"/>
-        <item x="979"/>
-        <item x="862"/>
-        <item x="93"/>
-        <item x="596"/>
-        <item x="383"/>
-        <item x="264"/>
-        <item x="875"/>
-        <item x="641"/>
-        <item x="978"/>
-        <item x="759"/>
-        <item x="234"/>
-        <item x="854"/>
-        <item x="51"/>
-        <item x="707"/>
-        <item x="100"/>
-        <item x="873"/>
-        <item x="655"/>
-        <item x="965"/>
-        <item x="542"/>
-        <item x="688"/>
-        <item x="391"/>
-        <item x="315"/>
-        <item x="727"/>
-        <item x="560"/>
-        <item x="176"/>
-        <item x="701"/>
-        <item x="865"/>
-        <item x="921"/>
-        <item x="311"/>
-        <item x="696"/>
-        <item x="379"/>
-        <item x="634"/>
-        <item x="712"/>
-        <item x="34"/>
-        <item x="417"/>
-        <item x="821"/>
-        <item x="908"/>
-        <item x="705"/>
-        <item x="454"/>
-        <item x="635"/>
-        <item x="127"/>
-        <item x="27"/>
-        <item x="984"/>
-        <item x="513"/>
-        <item x="809"/>
-        <item x="101"/>
-        <item x="667"/>
-        <item x="819"/>
-        <item x="130"/>
-        <item x="702"/>
-        <item x="443"/>
-        <item x="967"/>
-        <item x="693"/>
-        <item x="738"/>
-        <item x="556"/>
-        <item x="425"/>
-        <item x="63"/>
-        <item x="774"/>
-        <item x="954"/>
-        <item x="772"/>
-        <item x="370"/>
-        <item x="579"/>
-        <item x="511"/>
-        <item x="750"/>
-        <item x="552"/>
-        <item x="111"/>
-        <item x="728"/>
-        <item x="295"/>
-        <item x="236"/>
-        <item x="103"/>
-        <item x="549"/>
-        <item x="224"/>
-        <item x="153"/>
-        <item x="969"/>
-        <item x="243"/>
-        <item x="559"/>
-        <item x="122"/>
-        <item x="600"/>
-        <item x="518"/>
-        <item x="805"/>
-        <item x="976"/>
-        <item x="826"/>
-        <item x="91"/>
-        <item x="115"/>
-        <item x="1"/>
-        <item x="925"/>
-        <item x="287"/>
-        <item x="25"/>
-        <item x="314"/>
-        <item x="589"/>
-        <item x="112"/>
-        <item x="43"/>
-        <item x="68"/>
-        <item x="35"/>
-        <item x="469"/>
-        <item x="995"/>
-        <item x="461"/>
-        <item x="858"/>
-        <item x="166"/>
-        <item x="935"/>
-        <item x="446"/>
-        <item x="533"/>
-        <item x="402"/>
-        <item x="114"/>
-        <item x="830"/>
-        <item x="734"/>
-        <item x="149"/>
-        <item x="144"/>
-        <item x="220"/>
-        <item x="572"/>
-        <item x="568"/>
-        <item x="138"/>
-        <item x="685"/>
-        <item x="675"/>
-        <item x="54"/>
-        <item x="543"/>
-        <item x="932"/>
-        <item x="410"/>
-        <item x="481"/>
-        <item x="920"/>
-        <item x="730"/>
-        <item x="170"/>
-        <item x="758"/>
-        <item x="656"/>
-        <item x="13"/>
-        <item x="265"/>
-        <item x="369"/>
-        <item x="408"/>
-        <item x="960"/>
-        <item x="807"/>
-        <item x="436"/>
-        <item x="598"/>
-        <item x="715"/>
-        <item x="371"/>
-        <item x="148"/>
-        <item x="76"/>
-        <item x="793"/>
-        <item x="207"/>
-        <item x="691"/>
-        <item x="420"/>
-        <item x="988"/>
-        <item x="415"/>
-        <item x="713"/>
-        <item x="124"/>
-        <item x="233"/>
-        <item x="426"/>
-        <item x="839"/>
-        <item x="422"/>
-        <item x="364"/>
-        <item x="37"/>
-        <item x="22"/>
-        <item x="644"/>
-        <item x="677"/>
-        <item x="161"/>
-        <item x="325"/>
-        <item x="823"/>
-        <item x="611"/>
-        <item x="500"/>
-        <item x="586"/>
-        <item x="292"/>
-        <item x="223"/>
-        <item x="156"/>
-        <item x="141"/>
-        <item x="40"/>
-        <item x="503"/>
-        <item x="557"/>
-        <item x="288"/>
-        <item x="190"/>
-        <item x="613"/>
-        <item x="60"/>
-        <item x="306"/>
-        <item x="192"/>
-        <item x="526"/>
-        <item x="430"/>
-        <item x="74"/>
-        <item x="530"/>
-        <item x="754"/>
-        <item x="836"/>
-        <item x="380"/>
-        <item x="230"/>
-        <item x="253"/>
-        <item x="508"/>
-        <item x="116"/>
-        <item x="883"/>
-        <item x="841"/>
-        <item x="448"/>
-        <item x="729"/>
-        <item x="15"/>
-        <item x="20"/>
-        <item x="444"/>
-        <item x="423"/>
-        <item x="590"/>
-        <item x="996"/>
-        <item x="689"/>
-        <item x="186"/>
-        <item x="483"/>
-        <item x="951"/>
-        <item x="782"/>
-        <item x="298"/>
-        <item x="157"/>
-        <item x="629"/>
-        <item x="393"/>
-        <item x="538"/>
-        <item x="882"/>
-        <item x="910"/>
-        <item x="749"/>
-        <item x="7"/>
-        <item x="396"/>
-        <item x="171"/>
-        <item x="859"/>
-        <item x="293"/>
-        <item x="608"/>
-        <item x="89"/>
-        <item x="637"/>
-        <item x="19"/>
-        <item x="217"/>
-        <item x="463"/>
-        <item x="354"/>
-        <item x="681"/>
-        <item x="926"/>
-        <item x="660"/>
-        <item x="801"/>
-        <item x="961"/>
-        <item x="429"/>
-        <item x="886"/>
-        <item x="458"/>
-        <item x="462"/>
-        <item x="50"/>
-        <item x="616"/>
-        <item x="18"/>
-        <item x="944"/>
-        <item x="38"/>
-        <item x="599"/>
-        <item x="123"/>
-        <item x="142"/>
-        <item x="536"/>
-        <item x="582"/>
-        <item x="527"/>
-        <item x="575"/>
-        <item x="471"/>
-        <item x="329"/>
-        <item x="179"/>
-        <item x="571"/>
-        <item x="832"/>
-        <item x="541"/>
-        <item x="437"/>
-        <item x="744"/>
-        <item x="399"/>
-        <item x="238"/>
-        <item x="62"/>
-        <item x="998"/>
-        <item x="510"/>
-        <item x="609"/>
-        <item x="10"/>
-        <item x="42"/>
-        <item x="137"/>
-        <item x="573"/>
-        <item x="6"/>
-        <item x="555"/>
-        <item x="539"/>
-        <item x="583"/>
-        <item x="798"/>
-        <item x="84"/>
-        <item x="866"/>
-        <item x="937"/>
-        <item x="86"/>
-        <item x="638"/>
-        <item x="963"/>
-        <item x="949"/>
-        <item x="12"/>
-        <item x="820"/>
-        <item x="256"/>
-        <item x="650"/>
-        <item x="46"/>
-        <item x="682"/>
-        <item x="21"/>
-        <item x="409"/>
-        <item x="694"/>
-        <item x="322"/>
-        <item x="602"/>
-        <item x="742"/>
-        <item x="4"/>
-        <item x="948"/>
-        <item x="339"/>
-        <item x="985"/>
-        <item x="584"/>
-        <item x="244"/>
-        <item x="277"/>
-        <item x="900"/>
-        <item x="340"/>
-        <item x="119"/>
-        <item x="588"/>
-        <item x="811"/>
-        <item x="259"/>
-        <item x="77"/>
-        <item x="69"/>
-        <item x="373"/>
-        <item x="959"/>
-        <item x="736"/>
-        <item x="506"/>
-        <item x="767"/>
-        <item x="222"/>
-        <item x="890"/>
-        <item x="745"/>
-        <item x="580"/>
-        <item x="445"/>
-        <item x="70"/>
-        <item x="441"/>
-        <item x="388"/>
-        <item x="204"/>
-        <item x="690"/>
-        <item x="304"/>
-        <item x="927"/>
-        <item x="55"/>
-        <item x="553"/>
-        <item x="349"/>
-        <item x="188"/>
-        <item x="791"/>
-        <item x="154"/>
-        <item x="799"/>
-        <item x="498"/>
-        <item x="785"/>
-        <item x="472"/>
-        <item x="757"/>
-        <item x="178"/>
-        <item x="569"/>
-        <item x="668"/>
-        <item x="851"/>
-        <item x="897"/>
-        <item x="762"/>
-        <item x="305"/>
-        <item x="515"/>
-        <item x="174"/>
-        <item x="343"/>
-        <item x="829"/>
-        <item x="232"/>
-        <item x="720"/>
-        <item x="633"/>
-        <item x="199"/>
-        <item x="499"/>
-        <item x="620"/>
-        <item x="610"/>
-        <item x="374"/>
-        <item x="159"/>
-        <item x="313"/>
-        <item x="163"/>
-        <item x="516"/>
-        <item x="202"/>
-        <item x="834"/>
-        <item x="316"/>
-        <item x="957"/>
-        <item x="989"/>
-        <item x="289"/>
-        <item x="928"/>
-        <item x="936"/>
-        <item x="341"/>
-        <item x="724"/>
-        <item x="181"/>
-        <item x="531"/>
-        <item x="621"/>
-        <item x="494"/>
-        <item x="191"/>
-        <item x="485"/>
-        <item x="733"/>
-        <item x="303"/>
-        <item x="466"/>
-        <item x="346"/>
-        <item x="726"/>
-        <item x="333"/>
-        <item x="614"/>
-        <item x="796"/>
-        <item x="581"/>
-        <item x="709"/>
-        <item x="300"/>
-        <item x="263"/>
-        <item x="971"/>
-        <item x="878"/>
-        <item x="241"/>
-        <item x="943"/>
-        <item x="449"/>
-        <item x="440"/>
-        <item x="906"/>
-        <item x="521"/>
-        <item x="741"/>
-        <item x="972"/>
-        <item x="447"/>
-        <item x="912"/>
-        <item x="358"/>
-        <item x="924"/>
-        <item x="746"/>
-        <item x="779"/>
-        <item x="933"/>
-        <item x="145"/>
-        <item x="576"/>
-        <item x="914"/>
-        <item x="432"/>
-        <item x="540"/>
-        <item x="885"/>
-        <item x="363"/>
-        <item x="381"/>
-        <item x="228"/>
-        <item x="221"/>
-        <item x="367"/>
-        <item x="783"/>
-        <item x="595"/>
-        <item x="464"/>
-        <item x="773"/>
-        <item x="362"/>
-        <item x="414"/>
-        <item x="802"/>
-        <item x="274"/>
-        <item x="816"/>
-        <item x="239"/>
-        <item x="110"/>
-        <item x="82"/>
-        <item x="717"/>
-        <item x="134"/>
-        <item x="604"/>
-        <item x="476"/>
-        <item x="748"/>
-        <item x="143"/>
-        <item x="424"/>
-        <item x="945"/>
-        <item x="282"/>
-        <item x="880"/>
-        <item x="659"/>
-        <item x="484"/>
-        <item x="840"/>
-        <item x="789"/>
-        <item x="285"/>
-        <item x="815"/>
-        <item x="939"/>
-        <item x="934"/>
-        <item x="475"/>
-        <item x="514"/>
-        <item x="950"/>
-        <item x="88"/>
-        <item x="165"/>
-        <item x="901"/>
-        <item x="615"/>
-        <item x="491"/>
-        <item x="684"/>
-        <item x="72"/>
-        <item x="504"/>
-        <item x="94"/>
-        <item x="308"/>
-        <item x="564"/>
-        <item x="784"/>
-        <item x="665"/>
-        <item x="977"/>
-        <item x="517"/>
-        <item x="913"/>
-        <item x="281"/>
-        <item x="761"/>
-        <item x="385"/>
-        <item x="276"/>
-        <item x="335"/>
-        <item x="833"/>
-        <item x="680"/>
-        <item x="11"/>
-        <item x="245"/>
-        <item x="973"/>
-        <item x="348"/>
-        <item x="310"/>
-        <item x="457"/>
-        <item x="863"/>
-        <item x="524"/>
-        <item x="781"/>
-        <item x="278"/>
-        <item x="828"/>
-        <item x="548"/>
-        <item x="240"/>
-        <item x="480"/>
-        <item x="547"/>
-        <item x="390"/>
-        <item x="201"/>
-        <item x="607"/>
-        <item x="872"/>
-        <item x="904"/>
-        <item x="231"/>
-        <item x="743"/>
-        <item x="164"/>
-        <item x="884"/>
-        <item x="218"/>
-        <item x="843"/>
-        <item x="24"/>
-        <item x="129"/>
-        <item x="438"/>
-        <item x="574"/>
-        <item x="102"/>
-        <item x="987"/>
-        <item x="357"/>
-        <item x="467"/>
-        <item x="41"/>
-        <item x="673"/>
-        <item x="488"/>
-        <item x="195"/>
-        <item x="496"/>
-        <item x="966"/>
-        <item x="291"/>
-        <item x="808"/>
-        <item x="606"/>
-        <item x="216"/>
-        <item x="592"/>
-        <item x="657"/>
-        <item x="392"/>
-        <item x="651"/>
-        <item x="323"/>
-        <item x="284"/>
-        <item x="353"/>
-        <item x="90"/>
-        <item x="810"/>
-        <item x="275"/>
-        <item x="332"/>
-        <item x="453"/>
-        <item x="147"/>
-        <item x="411"/>
-        <item x="825"/>
-        <item x="267"/>
-        <item x="301"/>
-        <item x="208"/>
-        <item x="501"/>
-        <item x="49"/>
-        <item x="647"/>
-        <item x="431"/>
-        <item x="952"/>
-        <item x="139"/>
-        <item x="479"/>
-        <item x="672"/>
-        <item x="956"/>
-        <item x="359"/>
-        <item x="551"/>
-        <item x="535"/>
-        <item x="227"/>
-        <item x="871"/>
-        <item x="151"/>
-        <item x="294"/>
-        <item x="594"/>
-        <item x="751"/>
-        <item x="846"/>
-        <item x="184"/>
-        <item x="404"/>
-        <item x="763"/>
-        <item x="108"/>
-        <item x="670"/>
-        <item x="632"/>
-        <item x="133"/>
-        <item x="577"/>
-        <item x="723"/>
-        <item x="962"/>
-        <item x="765"/>
-        <item x="189"/>
-        <item x="286"/>
-        <item x="95"/>
-        <item x="33"/>
-        <item x="512"/>
-        <item x="378"/>
-        <item x="902"/>
-        <item x="389"/>
-        <item x="135"/>
-        <item x="624"/>
-        <item x="477"/>
-        <item x="519"/>
-        <item x="991"/>
-        <item x="509"/>
-        <item x="317"/>
-        <item x="247"/>
-        <item x="968"/>
-        <item x="361"/>
-        <item x="795"/>
-        <item x="200"/>
-        <item x="735"/>
-        <item x="892"/>
-        <item x="492"/>
-        <item x="877"/>
-        <item x="173"/>
-        <item x="150"/>
-        <item x="522"/>
-        <item x="636"/>
-        <item x="360"/>
-        <item x="368"/>
-        <item x="52"/>
-        <item x="433"/>
-        <item x="44"/>
-        <item x="806"/>
-        <item x="502"/>
-        <item x="321"/>
-        <item x="909"/>
-        <item x="700"/>
-        <item x="489"/>
-        <item x="106"/>
-        <item x="627"/>
-        <item x="780"/>
-        <item x="107"/>
-        <item x="868"/>
-        <item x="2"/>
-        <item x="495"/>
-        <item x="356"/>
-        <item x="338"/>
-        <item x="87"/>
-        <item x="273"/>
-        <item x="331"/>
-        <item x="731"/>
-        <item x="57"/>
-        <item x="831"/>
-        <item x="23"/>
-        <item x="919"/>
-        <item x="120"/>
-        <item x="460"/>
-        <item x="704"/>
-        <item x="32"/>
-        <item x="193"/>
-        <item x="663"/>
-        <item x="930"/>
-        <item x="619"/>
-        <item x="603"/>
-        <item x="118"/>
-        <item x="671"/>
-        <item x="537"/>
-        <item x="113"/>
-        <item x="235"/>
-        <item x="546"/>
-        <item x="687"/>
-        <item x="678"/>
-        <item x="320"/>
-        <item x="26"/>
-        <item x="427"/>
-        <item x="401"/>
-        <item x="567"/>
-        <item x="790"/>
-        <item x="755"/>
-        <item x="994"/>
-        <item x="631"/>
-        <item x="262"/>
-        <item x="213"/>
-        <item x="16"/>
-        <item x="852"/>
-        <item x="121"/>
-        <item x="117"/>
-        <item x="838"/>
-        <item x="251"/>
-        <item x="384"/>
-        <item x="128"/>
-        <item x="747"/>
-        <item x="8"/>
-        <item x="639"/>
-        <item x="375"/>
-        <item x="283"/>
-        <item x="125"/>
-        <item x="48"/>
-        <item x="837"/>
-        <item x="622"/>
-        <item x="206"/>
-        <item x="482"/>
-        <item x="813"/>
-        <item x="947"/>
-        <item x="474"/>
-        <item x="211"/>
-        <item x="721"/>
-        <item x="669"/>
-        <item x="146"/>
-        <item x="490"/>
-        <item x="271"/>
-        <item x="167"/>
-        <item x="692"/>
-        <item x="386"/>
-        <item x="993"/>
-        <item x="337"/>
-        <item x="9"/>
-        <item x="640"/>
-        <item x="587"/>
-        <item x="132"/>
-        <item x="413"/>
-        <item x="565"/>
-        <item x="198"/>
-        <item x="5"/>
-        <item x="895"/>
-        <item x="136"/>
-        <item x="545"/>
-        <item x="478"/>
-        <item x="794"/>
-        <item x="941"/>
-        <item x="788"/>
-        <item x="254"/>
-        <item x="318"/>
-        <item x="105"/>
-        <item x="645"/>
-        <item x="770"/>
-        <item x="486"/>
-        <item x="456"/>
-        <item x="768"/>
-        <item x="558"/>
-        <item x="664"/>
-        <item x="893"/>
-        <item x="104"/>
-        <item x="915"/>
-        <item x="566"/>
-        <item x="327"/>
-        <item x="525"/>
-        <item x="940"/>
-        <item x="229"/>
-        <item x="916"/>
-        <item x="407"/>
-        <item x="898"/>
-        <item x="387"/>
-        <item x="662"/>
-        <item x="347"/>
-        <item x="395"/>
-        <item x="505"/>
-        <item x="997"/>
-        <item x="452"/>
-        <item x="47"/>
-        <item x="296"/>
-        <item x="980"/>
-        <item x="711"/>
-        <item x="703"/>
-        <item x="257"/>
-        <item x="459"/>
-        <item x="85"/>
-        <item x="328"/>
-        <item x="372"/>
-        <item x="269"/>
-        <item x="473"/>
-        <item x="140"/>
-        <item x="187"/>
-        <item x="406"/>
-        <item x="75"/>
-        <item x="99"/>
-        <item x="740"/>
-        <item x="172"/>
-        <item x="520"/>
-        <item x="302"/>
-        <item x="714"/>
-        <item x="874"/>
-        <item x="649"/>
-        <item x="421"/>
-        <item x="428"/>
-        <item x="652"/>
-        <item x="158"/>
-        <item x="377"/>
-        <item x="297"/>
-        <item x="451"/>
-        <item x="792"/>
-        <item x="974"/>
-        <item x="419"/>
-        <item x="992"/>
-        <item x="970"/>
-        <item x="468"/>
-        <item x="324"/>
-        <item x="225"/>
-        <item x="152"/>
-        <item x="550"/>
-        <item x="857"/>
-        <item x="205"/>
-        <item x="917"/>
-        <item x="416"/>
-        <item x="0"/>
-        <item x="800"/>
-        <item x="699"/>
-        <item x="435"/>
-        <item x="676"/>
-        <item x="237"/>
-        <item x="79"/>
-        <item x="732"/>
-        <item x="931"/>
-        <item x="803"/>
-        <item x="771"/>
-        <item x="708"/>
-        <item x="827"/>
-        <item x="397"/>
-        <item x="563"/>
-        <item x="879"/>
-        <item x="986"/>
-        <item x="17"/>
-        <item x="96"/>
-        <item x="470"/>
-        <item x="455"/>
-        <item x="686"/>
-        <item x="856"/>
-        <item x="753"/>
-        <item x="722"/>
-        <item x="918"/>
-        <item x="39"/>
-        <item x="814"/>
-        <item x="53"/>
-        <item x="646"/>
-        <item x="299"/>
-        <item x="666"/>
-        <item x="896"/>
-        <item x="155"/>
-        <item x="270"/>
-        <item x="953"/>
-        <item x="822"/>
-        <item x="249"/>
-        <item x="756"/>
-        <item x="710"/>
-        <item x="319"/>
-        <item x="83"/>
-        <item x="764"/>
-        <item x="591"/>
-        <item x="718"/>
-        <item x="612"/>
-        <item x="219"/>
-        <item x="787"/>
-        <item x="398"/>
-        <item x="642"/>
-        <item x="964"/>
-        <item x="487"/>
-        <item x="71"/>
-        <item x="168"/>
-        <item x="578"/>
-        <item x="248"/>
-        <item x="695"/>
-        <item x="766"/>
-        <item x="215"/>
-        <item x="131"/>
-        <item x="307"/>
-        <item x="61"/>
-        <item x="845"/>
-        <item x="739"/>
-        <item x="752"/>
-        <item x="835"/>
-        <item x="266"/>
-        <item x="981"/>
-        <item x="942"/>
-        <item x="439"/>
-        <item x="674"/>
-        <item x="894"/>
-        <item x="812"/>
-        <item x="326"/>
-        <item x="626"/>
-        <item x="658"/>
-        <item x="58"/>
-        <item x="209"/>
-        <item x="261"/>
-        <item x="719"/>
-        <item x="183"/>
-        <item x="929"/>
-        <item x="697"/>
-        <item x="175"/>
-        <item x="528"/>
-        <item x="529"/>
-        <item x="618"/>
-        <item x="279"/>
-        <item x="14"/>
-        <item x="78"/>
-        <item x="605"/>
-        <item x="194"/>
-        <item x="403"/>
-        <item x="804"/>
-        <item x="817"/>
-        <item x="365"/>
-        <item x="706"/>
-        <item x="351"/>
-        <item x="570"/>
-        <item x="334"/>
-        <item x="226"/>
-        <item x="434"/>
-        <item x="922"/>
-        <item x="66"/>
-        <item x="617"/>
-        <item x="861"/>
-        <item x="544"/>
-        <item x="73"/>
-        <item x="661"/>
-        <item x="760"/>
-        <item x="376"/>
-        <item x="850"/>
-        <item x="250"/>
-        <item x="848"/>
-        <item x="955"/>
-        <item x="81"/>
-        <item x="418"/>
-        <item x="196"/>
-        <item x="309"/>
-        <item x="29"/>
-        <item x="860"/>
-        <item x="999"/>
-        <item x="260"/>
-        <item x="182"/>
-        <item x="907"/>
-        <item x="623"/>
-        <item x="869"/>
-        <item x="64"/>
-        <item x="197"/>
-        <item x="628"/>
-        <item x="716"/>
-        <item x="532"/>
-        <item x="648"/>
-        <item x="946"/>
-        <item x="842"/>
-        <item x="350"/>
-        <item x="109"/>
-        <item x="507"/>
-        <item x="847"/>
-        <item x="497"/>
-        <item x="797"/>
-        <item x="903"/>
-        <item x="98"/>
-        <item x="246"/>
-        <item x="853"/>
-        <item x="561"/>
-        <item x="958"/>
-        <item x="698"/>
-        <item x="382"/>
-        <item x="330"/>
-        <item x="818"/>
-        <item x="126"/>
-        <item x="80"/>
-        <item x="312"/>
-        <item x="97"/>
-        <item x="30"/>
-        <item x="870"/>
-        <item x="92"/>
-        <item x="342"/>
-        <item x="777"/>
-        <item x="203"/>
-        <item x="65"/>
-        <item x="465"/>
-        <item x="593"/>
-        <item x="889"/>
-        <item x="601"/>
-        <item x="405"/>
-        <item x="252"/>
-        <item x="975"/>
-        <item x="887"/>
-        <item x="394"/>
-        <item x="876"/>
-        <item x="990"/>
-        <item x="769"/>
-        <item x="786"/>
-        <item x="923"/>
-        <item x="210"/>
-        <item x="355"/>
-        <item x="450"/>
-        <item x="214"/>
-        <item x="534"/>
-        <item x="160"/>
-        <item x="855"/>
-        <item x="185"/>
-        <item x="844"/>
-        <item x="336"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="1"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="90">
-        <item x="17"/>
-        <item x="56"/>
-        <item x="75"/>
-        <item x="72"/>
-        <item x="0"/>
-        <item x="47"/>
-        <item x="27"/>
-        <item x="66"/>
-        <item x="51"/>
-        <item x="8"/>
-        <item x="83"/>
-        <item x="52"/>
-        <item x="50"/>
-        <item x="78"/>
-        <item x="15"/>
-        <item x="65"/>
-        <item x="29"/>
-        <item x="68"/>
-        <item x="64"/>
-        <item x="40"/>
-        <item x="18"/>
-        <item x="49"/>
-        <item x="54"/>
-        <item x="46"/>
-        <item x="25"/>
-        <item x="53"/>
-        <item x="3"/>
-        <item x="26"/>
-        <item x="71"/>
-        <item x="74"/>
-        <item x="82"/>
-        <item x="60"/>
-        <item x="30"/>
-        <item x="36"/>
-        <item x="87"/>
-        <item x="63"/>
-        <item x="10"/>
-        <item x="13"/>
-        <item x="4"/>
-        <item x="57"/>
-        <item x="34"/>
-        <item x="48"/>
-        <item x="12"/>
-        <item x="77"/>
-        <item x="44"/>
-        <item x="42"/>
-        <item x="69"/>
-        <item x="21"/>
-        <item x="67"/>
-        <item x="88"/>
-        <item x="9"/>
-        <item x="81"/>
-        <item x="70"/>
-        <item x="55"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="84"/>
-        <item x="33"/>
-        <item x="38"/>
-        <item x="59"/>
-        <item x="22"/>
-        <item x="2"/>
-        <item x="31"/>
-        <item x="19"/>
-        <item x="43"/>
-        <item x="37"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="24"/>
-        <item x="16"/>
-        <item x="41"/>
-        <item x="45"/>
-        <item x="86"/>
-        <item x="20"/>
-        <item x="32"/>
-        <item x="85"/>
-        <item x="79"/>
-        <item x="35"/>
-        <item x="80"/>
-        <item x="76"/>
-        <item x="23"/>
-        <item x="28"/>
-        <item x="62"/>
-        <item x="5"/>
-        <item x="58"/>
-        <item x="39"/>
-        <item x="61"/>
-        <item x="14"/>
-        <item x="73"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="20" showAll="0"/>
-    <pivotField showAll="0" countASubtotal="1">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="countA"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" sortType="descending">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sales" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="13">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{81DC4A31-0BDF-4AA7-888F-6BFE593127CD}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="G8:H12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField showAll="0">
-      <items count="1001">
-        <item x="162"/>
-        <item x="867"/>
-        <item x="778"/>
-        <item x="776"/>
-        <item x="683"/>
-        <item x="169"/>
-        <item x="56"/>
-        <item x="67"/>
-        <item x="824"/>
-        <item x="400"/>
-        <item x="255"/>
-        <item x="891"/>
-        <item x="881"/>
-        <item x="352"/>
-        <item x="905"/>
-        <item x="59"/>
-        <item x="775"/>
-        <item x="366"/>
-        <item x="3"/>
-        <item x="597"/>
-        <item x="864"/>
-        <item x="849"/>
-        <item x="272"/>
-        <item x="585"/>
-        <item x="36"/>
-        <item x="679"/>
-        <item x="180"/>
-        <item x="643"/>
-        <item x="938"/>
-        <item x="412"/>
-        <item x="45"/>
-        <item x="523"/>
-        <item x="654"/>
-        <item x="562"/>
-        <item x="554"/>
-        <item x="625"/>
-        <item x="345"/>
-        <item x="280"/>
-        <item x="737"/>
-        <item x="888"/>
-        <item x="442"/>
-        <item x="290"/>
-        <item x="982"/>
-        <item x="177"/>
-        <item x="212"/>
-        <item x="242"/>
-        <item x="268"/>
-        <item x="28"/>
-        <item x="899"/>
-        <item x="983"/>
-        <item x="493"/>
-        <item x="725"/>
-        <item x="653"/>
-        <item x="630"/>
-        <item x="31"/>
-        <item x="344"/>
-        <item x="258"/>
-        <item x="911"/>
-        <item x="979"/>
-        <item x="862"/>
-        <item x="93"/>
-        <item x="596"/>
-        <item x="383"/>
-        <item x="264"/>
-        <item x="875"/>
-        <item x="641"/>
-        <item x="978"/>
-        <item x="759"/>
-        <item x="234"/>
-        <item x="854"/>
-        <item x="51"/>
-        <item x="707"/>
-        <item x="100"/>
-        <item x="873"/>
-        <item x="655"/>
-        <item x="965"/>
-        <item x="542"/>
-        <item x="688"/>
-        <item x="391"/>
-        <item x="315"/>
-        <item x="727"/>
-        <item x="560"/>
-        <item x="176"/>
-        <item x="701"/>
-        <item x="865"/>
-        <item x="921"/>
-        <item x="311"/>
-        <item x="696"/>
-        <item x="379"/>
-        <item x="634"/>
-        <item x="712"/>
-        <item x="34"/>
-        <item x="417"/>
-        <item x="821"/>
-        <item x="908"/>
-        <item x="705"/>
-        <item x="454"/>
-        <item x="635"/>
-        <item x="127"/>
-        <item x="27"/>
-        <item x="984"/>
-        <item x="513"/>
-        <item x="809"/>
-        <item x="101"/>
-        <item x="667"/>
-        <item x="819"/>
-        <item x="130"/>
-        <item x="702"/>
-        <item x="443"/>
-        <item x="967"/>
-        <item x="693"/>
-        <item x="738"/>
-        <item x="556"/>
-        <item x="425"/>
-        <item x="63"/>
-        <item x="774"/>
-        <item x="954"/>
-        <item x="772"/>
-        <item x="370"/>
-        <item x="579"/>
-        <item x="511"/>
-        <item x="750"/>
-        <item x="552"/>
-        <item x="111"/>
-        <item x="728"/>
-        <item x="295"/>
-        <item x="236"/>
-        <item x="103"/>
-        <item x="549"/>
-        <item x="224"/>
-        <item x="153"/>
-        <item x="969"/>
-        <item x="243"/>
-        <item x="559"/>
-        <item x="122"/>
-        <item x="600"/>
-        <item x="518"/>
-        <item x="805"/>
-        <item x="976"/>
-        <item x="826"/>
-        <item x="91"/>
-        <item x="115"/>
-        <item x="1"/>
-        <item x="925"/>
-        <item x="287"/>
-        <item x="25"/>
-        <item x="314"/>
-        <item x="589"/>
-        <item x="112"/>
-        <item x="43"/>
-        <item x="68"/>
-        <item x="35"/>
-        <item x="469"/>
-        <item x="995"/>
-        <item x="461"/>
-        <item x="858"/>
-        <item x="166"/>
-        <item x="935"/>
-        <item x="446"/>
-        <item x="533"/>
-        <item x="402"/>
-        <item x="114"/>
-        <item x="830"/>
-        <item x="734"/>
-        <item x="149"/>
-        <item x="144"/>
-        <item x="220"/>
-        <item x="572"/>
-        <item x="568"/>
-        <item x="138"/>
-        <item x="685"/>
-        <item x="675"/>
-        <item x="54"/>
-        <item x="543"/>
-        <item x="932"/>
-        <item x="410"/>
-        <item x="481"/>
-        <item x="920"/>
-        <item x="730"/>
-        <item x="170"/>
-        <item x="758"/>
-        <item x="656"/>
-        <item x="13"/>
-        <item x="265"/>
-        <item x="369"/>
-        <item x="408"/>
-        <item x="960"/>
-        <item x="807"/>
-        <item x="436"/>
-        <item x="598"/>
-        <item x="715"/>
-        <item x="371"/>
-        <item x="148"/>
-        <item x="76"/>
-        <item x="793"/>
-        <item x="207"/>
-        <item x="691"/>
-        <item x="420"/>
-        <item x="988"/>
-        <item x="415"/>
-        <item x="713"/>
-        <item x="124"/>
-        <item x="233"/>
-        <item x="426"/>
-        <item x="839"/>
-        <item x="422"/>
-        <item x="364"/>
-        <item x="37"/>
-        <item x="22"/>
-        <item x="644"/>
-        <item x="677"/>
-        <item x="161"/>
-        <item x="325"/>
-        <item x="823"/>
-        <item x="611"/>
-        <item x="500"/>
-        <item x="586"/>
-        <item x="292"/>
-        <item x="223"/>
-        <item x="156"/>
-        <item x="141"/>
-        <item x="40"/>
-        <item x="503"/>
-        <item x="557"/>
-        <item x="288"/>
-        <item x="190"/>
-        <item x="613"/>
-        <item x="60"/>
-        <item x="306"/>
-        <item x="192"/>
-        <item x="526"/>
-        <item x="430"/>
-        <item x="74"/>
-        <item x="530"/>
-        <item x="754"/>
-        <item x="836"/>
-        <item x="380"/>
-        <item x="230"/>
-        <item x="253"/>
-        <item x="508"/>
-        <item x="116"/>
-        <item x="883"/>
-        <item x="841"/>
-        <item x="448"/>
-        <item x="729"/>
-        <item x="15"/>
-        <item x="20"/>
-        <item x="444"/>
-        <item x="423"/>
-        <item x="590"/>
-        <item x="996"/>
-        <item x="689"/>
-        <item x="186"/>
-        <item x="483"/>
-        <item x="951"/>
-        <item x="782"/>
-        <item x="298"/>
-        <item x="157"/>
-        <item x="629"/>
-        <item x="393"/>
-        <item x="538"/>
-        <item x="882"/>
-        <item x="910"/>
-        <item x="749"/>
-        <item x="7"/>
-        <item x="396"/>
-        <item x="171"/>
-        <item x="859"/>
-        <item x="293"/>
-        <item x="608"/>
-        <item x="89"/>
-        <item x="637"/>
-        <item x="19"/>
-        <item x="217"/>
-        <item x="463"/>
-        <item x="354"/>
-        <item x="681"/>
-        <item x="926"/>
-        <item x="660"/>
-        <item x="801"/>
-        <item x="961"/>
-        <item x="429"/>
-        <item x="886"/>
-        <item x="458"/>
-        <item x="462"/>
-        <item x="50"/>
-        <item x="616"/>
-        <item x="18"/>
-        <item x="944"/>
-        <item x="38"/>
-        <item x="599"/>
-        <item x="123"/>
-        <item x="142"/>
-        <item x="536"/>
-        <item x="582"/>
-        <item x="527"/>
-        <item x="575"/>
-        <item x="471"/>
-        <item x="329"/>
-        <item x="179"/>
-        <item x="571"/>
-        <item x="832"/>
-        <item x="541"/>
-        <item x="437"/>
-        <item x="744"/>
-        <item x="399"/>
-        <item x="238"/>
-        <item x="62"/>
-        <item x="998"/>
-        <item x="510"/>
-        <item x="609"/>
-        <item x="10"/>
-        <item x="42"/>
-        <item x="137"/>
-        <item x="573"/>
-        <item x="6"/>
-        <item x="555"/>
-        <item x="539"/>
-        <item x="583"/>
-        <item x="798"/>
-        <item x="84"/>
-        <item x="866"/>
-        <item x="937"/>
-        <item x="86"/>
-        <item x="638"/>
-        <item x="963"/>
-        <item x="949"/>
-        <item x="12"/>
-        <item x="820"/>
-        <item x="256"/>
-        <item x="650"/>
-        <item x="46"/>
-        <item x="682"/>
-        <item x="21"/>
-        <item x="409"/>
-        <item x="694"/>
-        <item x="322"/>
-        <item x="602"/>
-        <item x="742"/>
-        <item x="4"/>
-        <item x="948"/>
-        <item x="339"/>
-        <item x="985"/>
-        <item x="584"/>
-        <item x="244"/>
-        <item x="277"/>
-        <item x="900"/>
-        <item x="340"/>
-        <item x="119"/>
-        <item x="588"/>
-        <item x="811"/>
-        <item x="259"/>
-        <item x="77"/>
-        <item x="69"/>
-        <item x="373"/>
-        <item x="959"/>
-        <item x="736"/>
-        <item x="506"/>
-        <item x="767"/>
-        <item x="222"/>
-        <item x="890"/>
-        <item x="745"/>
-        <item x="580"/>
-        <item x="445"/>
-        <item x="70"/>
-        <item x="441"/>
-        <item x="388"/>
-        <item x="204"/>
-        <item x="690"/>
-        <item x="304"/>
-        <item x="927"/>
-        <item x="55"/>
-        <item x="553"/>
-        <item x="349"/>
-        <item x="188"/>
-        <item x="791"/>
-        <item x="154"/>
-        <item x="799"/>
-        <item x="498"/>
-        <item x="785"/>
-        <item x="472"/>
-        <item x="757"/>
-        <item x="178"/>
-        <item x="569"/>
-        <item x="668"/>
-        <item x="851"/>
-        <item x="897"/>
-        <item x="762"/>
-        <item x="305"/>
-        <item x="515"/>
-        <item x="174"/>
-        <item x="343"/>
-        <item x="829"/>
-        <item x="232"/>
-        <item x="720"/>
-        <item x="633"/>
-        <item x="199"/>
-        <item x="499"/>
-        <item x="620"/>
-        <item x="610"/>
-        <item x="374"/>
-        <item x="159"/>
-        <item x="313"/>
-        <item x="163"/>
-        <item x="516"/>
-        <item x="202"/>
-        <item x="834"/>
-        <item x="316"/>
-        <item x="957"/>
-        <item x="989"/>
-        <item x="289"/>
-        <item x="928"/>
-        <item x="936"/>
-        <item x="341"/>
-        <item x="724"/>
-        <item x="181"/>
-        <item x="531"/>
-        <item x="621"/>
-        <item x="494"/>
-        <item x="191"/>
-        <item x="485"/>
-        <item x="733"/>
-        <item x="303"/>
-        <item x="466"/>
-        <item x="346"/>
-        <item x="726"/>
-        <item x="333"/>
-        <item x="614"/>
-        <item x="796"/>
-        <item x="581"/>
-        <item x="709"/>
-        <item x="300"/>
-        <item x="263"/>
-        <item x="971"/>
-        <item x="878"/>
-        <item x="241"/>
-        <item x="943"/>
-        <item x="449"/>
-        <item x="440"/>
-        <item x="906"/>
-        <item x="521"/>
-        <item x="741"/>
-        <item x="972"/>
-        <item x="447"/>
-        <item x="912"/>
-        <item x="358"/>
-        <item x="924"/>
-        <item x="746"/>
-        <item x="779"/>
-        <item x="933"/>
-        <item x="145"/>
-        <item x="576"/>
-        <item x="914"/>
-        <item x="432"/>
-        <item x="540"/>
-        <item x="885"/>
-        <item x="363"/>
-        <item x="381"/>
-        <item x="228"/>
-        <item x="221"/>
-        <item x="367"/>
-        <item x="783"/>
-        <item x="595"/>
-        <item x="464"/>
-        <item x="773"/>
-        <item x="362"/>
-        <item x="414"/>
-        <item x="802"/>
-        <item x="274"/>
-        <item x="816"/>
-        <item x="239"/>
-        <item x="110"/>
-        <item x="82"/>
-        <item x="717"/>
-        <item x="134"/>
-        <item x="604"/>
-        <item x="476"/>
-        <item x="748"/>
-        <item x="143"/>
-        <item x="424"/>
-        <item x="945"/>
-        <item x="282"/>
-        <item x="880"/>
-        <item x="659"/>
-        <item x="484"/>
-        <item x="840"/>
-        <item x="789"/>
-        <item x="285"/>
-        <item x="815"/>
-        <item x="939"/>
-        <item x="934"/>
-        <item x="475"/>
-        <item x="514"/>
-        <item x="950"/>
-        <item x="88"/>
-        <item x="165"/>
-        <item x="901"/>
-        <item x="615"/>
-        <item x="491"/>
-        <item x="684"/>
-        <item x="72"/>
-        <item x="504"/>
-        <item x="94"/>
-        <item x="308"/>
-        <item x="564"/>
-        <item x="784"/>
-        <item x="665"/>
-        <item x="977"/>
-        <item x="517"/>
-        <item x="913"/>
-        <item x="281"/>
-        <item x="761"/>
-        <item x="385"/>
-        <item x="276"/>
-        <item x="335"/>
-        <item x="833"/>
-        <item x="680"/>
-        <item x="11"/>
-        <item x="245"/>
-        <item x="973"/>
-        <item x="348"/>
-        <item x="310"/>
-        <item x="457"/>
-        <item x="863"/>
-        <item x="524"/>
-        <item x="781"/>
-        <item x="278"/>
-        <item x="828"/>
-        <item x="548"/>
-        <item x="240"/>
-        <item x="480"/>
-        <item x="547"/>
-        <item x="390"/>
-        <item x="201"/>
-        <item x="607"/>
-        <item x="872"/>
-        <item x="904"/>
-        <item x="231"/>
-        <item x="743"/>
-        <item x="164"/>
-        <item x="884"/>
-        <item x="218"/>
-        <item x="843"/>
-        <item x="24"/>
-        <item x="129"/>
-        <item x="438"/>
-        <item x="574"/>
-        <item x="102"/>
-        <item x="987"/>
-        <item x="357"/>
-        <item x="467"/>
-        <item x="41"/>
-        <item x="673"/>
-        <item x="488"/>
-        <item x="195"/>
-        <item x="496"/>
-        <item x="966"/>
-        <item x="291"/>
-        <item x="808"/>
-        <item x="606"/>
-        <item x="216"/>
-        <item x="592"/>
-        <item x="657"/>
-        <item x="392"/>
-        <item x="651"/>
-        <item x="323"/>
-        <item x="284"/>
-        <item x="353"/>
-        <item x="90"/>
-        <item x="810"/>
-        <item x="275"/>
-        <item x="332"/>
-        <item x="453"/>
-        <item x="147"/>
-        <item x="411"/>
-        <item x="825"/>
-        <item x="267"/>
-        <item x="301"/>
-        <item x="208"/>
-        <item x="501"/>
-        <item x="49"/>
-        <item x="647"/>
-        <item x="431"/>
-        <item x="952"/>
-        <item x="139"/>
-        <item x="479"/>
-        <item x="672"/>
-        <item x="956"/>
-        <item x="359"/>
-        <item x="551"/>
-        <item x="535"/>
-        <item x="227"/>
-        <item x="871"/>
-        <item x="151"/>
-        <item x="294"/>
-        <item x="594"/>
-        <item x="751"/>
-        <item x="846"/>
-        <item x="184"/>
-        <item x="404"/>
-        <item x="763"/>
-        <item x="108"/>
-        <item x="670"/>
-        <item x="632"/>
-        <item x="133"/>
-        <item x="577"/>
-        <item x="723"/>
-        <item x="962"/>
-        <item x="765"/>
-        <item x="189"/>
-        <item x="286"/>
-        <item x="95"/>
-        <item x="33"/>
-        <item x="512"/>
-        <item x="378"/>
-        <item x="902"/>
-        <item x="389"/>
-        <item x="135"/>
-        <item x="624"/>
-        <item x="477"/>
-        <item x="519"/>
-        <item x="991"/>
-        <item x="509"/>
-        <item x="317"/>
-        <item x="247"/>
-        <item x="968"/>
-        <item x="361"/>
-        <item x="795"/>
-        <item x="200"/>
-        <item x="735"/>
-        <item x="892"/>
-        <item x="492"/>
-        <item x="877"/>
-        <item x="173"/>
-        <item x="150"/>
-        <item x="522"/>
-        <item x="636"/>
-        <item x="360"/>
-        <item x="368"/>
-        <item x="52"/>
-        <item x="433"/>
-        <item x="44"/>
-        <item x="806"/>
-        <item x="502"/>
-        <item x="321"/>
-        <item x="909"/>
-        <item x="700"/>
-        <item x="489"/>
-        <item x="106"/>
-        <item x="627"/>
-        <item x="780"/>
-        <item x="107"/>
-        <item x="868"/>
-        <item x="2"/>
-        <item x="495"/>
-        <item x="356"/>
-        <item x="338"/>
-        <item x="87"/>
-        <item x="273"/>
-        <item x="331"/>
-        <item x="731"/>
-        <item x="57"/>
-        <item x="831"/>
-        <item x="23"/>
-        <item x="919"/>
-        <item x="120"/>
-        <item x="460"/>
-        <item x="704"/>
-        <item x="32"/>
-        <item x="193"/>
-        <item x="663"/>
-        <item x="930"/>
-        <item x="619"/>
-        <item x="603"/>
-        <item x="118"/>
-        <item x="671"/>
-        <item x="537"/>
-        <item x="113"/>
-        <item x="235"/>
-        <item x="546"/>
-        <item x="687"/>
-        <item x="678"/>
-        <item x="320"/>
-        <item x="26"/>
-        <item x="427"/>
-        <item x="401"/>
-        <item x="567"/>
-        <item x="790"/>
-        <item x="755"/>
-        <item x="994"/>
-        <item x="631"/>
-        <item x="262"/>
-        <item x="213"/>
-        <item x="16"/>
-        <item x="852"/>
-        <item x="121"/>
-        <item x="117"/>
-        <item x="838"/>
-        <item x="251"/>
-        <item x="384"/>
-        <item x="128"/>
-        <item x="747"/>
-        <item x="8"/>
-        <item x="639"/>
-        <item x="375"/>
-        <item x="283"/>
-        <item x="125"/>
-        <item x="48"/>
-        <item x="837"/>
-        <item x="622"/>
-        <item x="206"/>
-        <item x="482"/>
-        <item x="813"/>
-        <item x="947"/>
-        <item x="474"/>
-        <item x="211"/>
-        <item x="721"/>
-        <item x="669"/>
-        <item x="146"/>
-        <item x="490"/>
-        <item x="271"/>
-        <item x="167"/>
-        <item x="692"/>
-        <item x="386"/>
-        <item x="993"/>
-        <item x="337"/>
-        <item x="9"/>
-        <item x="640"/>
-        <item x="587"/>
-        <item x="132"/>
-        <item x="413"/>
-        <item x="565"/>
-        <item x="198"/>
-        <item x="5"/>
-        <item x="895"/>
-        <item x="136"/>
-        <item x="545"/>
-        <item x="478"/>
-        <item x="794"/>
-        <item x="941"/>
-        <item x="788"/>
-        <item x="254"/>
-        <item x="318"/>
-        <item x="105"/>
-        <item x="645"/>
-        <item x="770"/>
-        <item x="486"/>
-        <item x="456"/>
-        <item x="768"/>
-        <item x="558"/>
-        <item x="664"/>
-        <item x="893"/>
-        <item x="104"/>
-        <item x="915"/>
-        <item x="566"/>
-        <item x="327"/>
-        <item x="525"/>
-        <item x="940"/>
-        <item x="229"/>
-        <item x="916"/>
-        <item x="407"/>
-        <item x="898"/>
-        <item x="387"/>
-        <item x="662"/>
-        <item x="347"/>
-        <item x="395"/>
-        <item x="505"/>
-        <item x="997"/>
-        <item x="452"/>
-        <item x="47"/>
-        <item x="296"/>
-        <item x="980"/>
-        <item x="711"/>
-        <item x="703"/>
-        <item x="257"/>
-        <item x="459"/>
-        <item x="85"/>
-        <item x="328"/>
-        <item x="372"/>
-        <item x="269"/>
-        <item x="473"/>
-        <item x="140"/>
-        <item x="187"/>
-        <item x="406"/>
-        <item x="75"/>
-        <item x="99"/>
-        <item x="740"/>
-        <item x="172"/>
-        <item x="520"/>
-        <item x="302"/>
-        <item x="714"/>
-        <item x="874"/>
-        <item x="649"/>
-        <item x="421"/>
-        <item x="428"/>
-        <item x="652"/>
-        <item x="158"/>
-        <item x="377"/>
-        <item x="297"/>
-        <item x="451"/>
-        <item x="792"/>
-        <item x="974"/>
-        <item x="419"/>
-        <item x="992"/>
-        <item x="970"/>
-        <item x="468"/>
-        <item x="324"/>
-        <item x="225"/>
-        <item x="152"/>
-        <item x="550"/>
-        <item x="857"/>
-        <item x="205"/>
-        <item x="917"/>
-        <item x="416"/>
-        <item x="0"/>
-        <item x="800"/>
-        <item x="699"/>
-        <item x="435"/>
-        <item x="676"/>
-        <item x="237"/>
-        <item x="79"/>
-        <item x="732"/>
-        <item x="931"/>
-        <item x="803"/>
-        <item x="771"/>
-        <item x="708"/>
-        <item x="827"/>
-        <item x="397"/>
-        <item x="563"/>
-        <item x="879"/>
-        <item x="986"/>
-        <item x="17"/>
-        <item x="96"/>
-        <item x="470"/>
-        <item x="455"/>
-        <item x="686"/>
-        <item x="856"/>
-        <item x="753"/>
-        <item x="722"/>
-        <item x="918"/>
-        <item x="39"/>
-        <item x="814"/>
-        <item x="53"/>
-        <item x="646"/>
-        <item x="299"/>
-        <item x="666"/>
-        <item x="896"/>
-        <item x="155"/>
-        <item x="270"/>
-        <item x="953"/>
-        <item x="822"/>
-        <item x="249"/>
-        <item x="756"/>
-        <item x="710"/>
-        <item x="319"/>
-        <item x="83"/>
-        <item x="764"/>
-        <item x="591"/>
-        <item x="718"/>
-        <item x="612"/>
-        <item x="219"/>
-        <item x="787"/>
-        <item x="398"/>
-        <item x="642"/>
-        <item x="964"/>
-        <item x="487"/>
-        <item x="71"/>
-        <item x="168"/>
-        <item x="578"/>
-        <item x="248"/>
-        <item x="695"/>
-        <item x="766"/>
-        <item x="215"/>
-        <item x="131"/>
-        <item x="307"/>
-        <item x="61"/>
-        <item x="845"/>
-        <item x="739"/>
-        <item x="752"/>
-        <item x="835"/>
-        <item x="266"/>
-        <item x="981"/>
-        <item x="942"/>
-        <item x="439"/>
-        <item x="674"/>
-        <item x="894"/>
-        <item x="812"/>
-        <item x="326"/>
-        <item x="626"/>
-        <item x="658"/>
-        <item x="58"/>
-        <item x="209"/>
-        <item x="261"/>
-        <item x="719"/>
-        <item x="183"/>
-        <item x="929"/>
-        <item x="697"/>
-        <item x="175"/>
-        <item x="528"/>
-        <item x="529"/>
-        <item x="618"/>
-        <item x="279"/>
-        <item x="14"/>
-        <item x="78"/>
-        <item x="605"/>
-        <item x="194"/>
-        <item x="403"/>
-        <item x="804"/>
-        <item x="817"/>
-        <item x="365"/>
-        <item x="706"/>
-        <item x="351"/>
-        <item x="570"/>
-        <item x="334"/>
-        <item x="226"/>
-        <item x="434"/>
-        <item x="922"/>
-        <item x="66"/>
-        <item x="617"/>
-        <item x="861"/>
-        <item x="544"/>
-        <item x="73"/>
-        <item x="661"/>
-        <item x="760"/>
-        <item x="376"/>
-        <item x="850"/>
-        <item x="250"/>
-        <item x="848"/>
-        <item x="955"/>
-        <item x="81"/>
-        <item x="418"/>
-        <item x="196"/>
-        <item x="309"/>
-        <item x="29"/>
-        <item x="860"/>
-        <item x="999"/>
-        <item x="260"/>
-        <item x="182"/>
-        <item x="907"/>
-        <item x="623"/>
-        <item x="869"/>
-        <item x="64"/>
-        <item x="197"/>
-        <item x="628"/>
-        <item x="716"/>
-        <item x="532"/>
-        <item x="648"/>
-        <item x="946"/>
-        <item x="842"/>
-        <item x="350"/>
-        <item x="109"/>
-        <item x="507"/>
-        <item x="847"/>
-        <item x="497"/>
-        <item x="797"/>
-        <item x="903"/>
-        <item x="98"/>
-        <item x="246"/>
-        <item x="853"/>
-        <item x="561"/>
-        <item x="958"/>
-        <item x="698"/>
-        <item x="382"/>
-        <item x="330"/>
-        <item x="818"/>
-        <item x="126"/>
-        <item x="80"/>
-        <item x="312"/>
-        <item x="97"/>
-        <item x="30"/>
-        <item x="870"/>
-        <item x="92"/>
-        <item x="342"/>
-        <item x="777"/>
-        <item x="203"/>
-        <item x="65"/>
-        <item x="465"/>
-        <item x="593"/>
-        <item x="889"/>
-        <item x="601"/>
-        <item x="405"/>
-        <item x="252"/>
-        <item x="975"/>
-        <item x="887"/>
-        <item x="394"/>
-        <item x="876"/>
-        <item x="990"/>
-        <item x="769"/>
-        <item x="786"/>
-        <item x="923"/>
-        <item x="210"/>
-        <item x="355"/>
-        <item x="450"/>
-        <item x="214"/>
-        <item x="534"/>
-        <item x="160"/>
-        <item x="855"/>
-        <item x="185"/>
-        <item x="844"/>
-        <item x="336"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="1"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="90">
-        <item x="17"/>
-        <item x="56"/>
-        <item x="75"/>
-        <item x="72"/>
-        <item x="0"/>
-        <item x="47"/>
-        <item x="27"/>
-        <item x="66"/>
-        <item x="51"/>
-        <item x="8"/>
-        <item x="83"/>
-        <item x="52"/>
-        <item x="50"/>
-        <item x="78"/>
-        <item x="15"/>
-        <item x="65"/>
-        <item x="29"/>
-        <item x="68"/>
-        <item x="64"/>
-        <item x="40"/>
-        <item x="18"/>
-        <item x="49"/>
-        <item x="54"/>
-        <item x="46"/>
-        <item x="25"/>
-        <item x="53"/>
-        <item x="3"/>
-        <item x="26"/>
-        <item x="71"/>
-        <item x="74"/>
-        <item x="82"/>
-        <item x="60"/>
-        <item x="30"/>
-        <item x="36"/>
-        <item x="87"/>
-        <item x="63"/>
-        <item x="10"/>
-        <item x="13"/>
-        <item x="4"/>
-        <item x="57"/>
-        <item x="34"/>
-        <item x="48"/>
-        <item x="12"/>
-        <item x="77"/>
-        <item x="44"/>
-        <item x="42"/>
-        <item x="69"/>
-        <item x="21"/>
-        <item x="67"/>
-        <item x="88"/>
-        <item x="9"/>
-        <item x="81"/>
-        <item x="70"/>
-        <item x="55"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="84"/>
-        <item x="33"/>
-        <item x="38"/>
-        <item x="59"/>
-        <item x="22"/>
-        <item x="2"/>
-        <item x="31"/>
-        <item x="19"/>
-        <item x="43"/>
-        <item x="37"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="24"/>
-        <item x="16"/>
-        <item x="41"/>
-        <item x="45"/>
-        <item x="86"/>
-        <item x="20"/>
-        <item x="32"/>
-        <item x="85"/>
-        <item x="79"/>
-        <item x="35"/>
-        <item x="80"/>
-        <item x="76"/>
-        <item x="23"/>
-        <item x="28"/>
-        <item x="62"/>
-        <item x="5"/>
-        <item x="58"/>
-        <item x="39"/>
-        <item x="61"/>
-        <item x="14"/>
-        <item x="73"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="20" showAll="0"/>
-    <pivotField showAll="0" countASubtotal="1">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="countA"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="15">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="0"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="15"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sales" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="14">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="15" count="3">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{092325F4-39D2-4190-A2C2-221ADDB84F82}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E4" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="16">
@@ -39884,8 +41378,8 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="4">
-        <item x="0"/>
-        <item x="2"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -40066,7 +41560,7 @@
     <dataField name="Total Quantity" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="15">
+    <format dxfId="107">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -40076,1267 +41570,6 @@
       </pivotArea>
     </format>
   </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CBF87619-36E8-492C-98AD-E06666849A62}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="D16:E20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField showAll="0">
-      <items count="1001">
-        <item x="162"/>
-        <item x="867"/>
-        <item x="778"/>
-        <item x="776"/>
-        <item x="683"/>
-        <item x="169"/>
-        <item x="56"/>
-        <item x="67"/>
-        <item x="824"/>
-        <item x="400"/>
-        <item x="255"/>
-        <item x="891"/>
-        <item x="881"/>
-        <item x="352"/>
-        <item x="905"/>
-        <item x="59"/>
-        <item x="775"/>
-        <item x="366"/>
-        <item x="3"/>
-        <item x="597"/>
-        <item x="864"/>
-        <item x="849"/>
-        <item x="272"/>
-        <item x="585"/>
-        <item x="36"/>
-        <item x="679"/>
-        <item x="180"/>
-        <item x="643"/>
-        <item x="938"/>
-        <item x="412"/>
-        <item x="45"/>
-        <item x="523"/>
-        <item x="654"/>
-        <item x="562"/>
-        <item x="554"/>
-        <item x="625"/>
-        <item x="345"/>
-        <item x="280"/>
-        <item x="737"/>
-        <item x="888"/>
-        <item x="442"/>
-        <item x="290"/>
-        <item x="982"/>
-        <item x="177"/>
-        <item x="212"/>
-        <item x="242"/>
-        <item x="268"/>
-        <item x="28"/>
-        <item x="899"/>
-        <item x="983"/>
-        <item x="493"/>
-        <item x="725"/>
-        <item x="653"/>
-        <item x="630"/>
-        <item x="31"/>
-        <item x="344"/>
-        <item x="258"/>
-        <item x="911"/>
-        <item x="979"/>
-        <item x="862"/>
-        <item x="93"/>
-        <item x="596"/>
-        <item x="383"/>
-        <item x="264"/>
-        <item x="875"/>
-        <item x="641"/>
-        <item x="978"/>
-        <item x="759"/>
-        <item x="234"/>
-        <item x="854"/>
-        <item x="51"/>
-        <item x="707"/>
-        <item x="100"/>
-        <item x="873"/>
-        <item x="655"/>
-        <item x="965"/>
-        <item x="542"/>
-        <item x="688"/>
-        <item x="391"/>
-        <item x="315"/>
-        <item x="727"/>
-        <item x="560"/>
-        <item x="176"/>
-        <item x="701"/>
-        <item x="865"/>
-        <item x="921"/>
-        <item x="311"/>
-        <item x="696"/>
-        <item x="379"/>
-        <item x="634"/>
-        <item x="712"/>
-        <item x="34"/>
-        <item x="417"/>
-        <item x="821"/>
-        <item x="908"/>
-        <item x="705"/>
-        <item x="454"/>
-        <item x="635"/>
-        <item x="127"/>
-        <item x="27"/>
-        <item x="984"/>
-        <item x="513"/>
-        <item x="809"/>
-        <item x="101"/>
-        <item x="667"/>
-        <item x="819"/>
-        <item x="130"/>
-        <item x="702"/>
-        <item x="443"/>
-        <item x="967"/>
-        <item x="693"/>
-        <item x="738"/>
-        <item x="556"/>
-        <item x="425"/>
-        <item x="63"/>
-        <item x="774"/>
-        <item x="954"/>
-        <item x="772"/>
-        <item x="370"/>
-        <item x="579"/>
-        <item x="511"/>
-        <item x="750"/>
-        <item x="552"/>
-        <item x="111"/>
-        <item x="728"/>
-        <item x="295"/>
-        <item x="236"/>
-        <item x="103"/>
-        <item x="549"/>
-        <item x="224"/>
-        <item x="153"/>
-        <item x="969"/>
-        <item x="243"/>
-        <item x="559"/>
-        <item x="122"/>
-        <item x="600"/>
-        <item x="518"/>
-        <item x="805"/>
-        <item x="976"/>
-        <item x="826"/>
-        <item x="91"/>
-        <item x="115"/>
-        <item x="1"/>
-        <item x="925"/>
-        <item x="287"/>
-        <item x="25"/>
-        <item x="314"/>
-        <item x="589"/>
-        <item x="112"/>
-        <item x="43"/>
-        <item x="68"/>
-        <item x="35"/>
-        <item x="469"/>
-        <item x="995"/>
-        <item x="461"/>
-        <item x="858"/>
-        <item x="166"/>
-        <item x="935"/>
-        <item x="446"/>
-        <item x="533"/>
-        <item x="402"/>
-        <item x="114"/>
-        <item x="830"/>
-        <item x="734"/>
-        <item x="149"/>
-        <item x="144"/>
-        <item x="220"/>
-        <item x="572"/>
-        <item x="568"/>
-        <item x="138"/>
-        <item x="685"/>
-        <item x="675"/>
-        <item x="54"/>
-        <item x="543"/>
-        <item x="932"/>
-        <item x="410"/>
-        <item x="481"/>
-        <item x="920"/>
-        <item x="730"/>
-        <item x="170"/>
-        <item x="758"/>
-        <item x="656"/>
-        <item x="13"/>
-        <item x="265"/>
-        <item x="369"/>
-        <item x="408"/>
-        <item x="960"/>
-        <item x="807"/>
-        <item x="436"/>
-        <item x="598"/>
-        <item x="715"/>
-        <item x="371"/>
-        <item x="148"/>
-        <item x="76"/>
-        <item x="793"/>
-        <item x="207"/>
-        <item x="691"/>
-        <item x="420"/>
-        <item x="988"/>
-        <item x="415"/>
-        <item x="713"/>
-        <item x="124"/>
-        <item x="233"/>
-        <item x="426"/>
-        <item x="839"/>
-        <item x="422"/>
-        <item x="364"/>
-        <item x="37"/>
-        <item x="22"/>
-        <item x="644"/>
-        <item x="677"/>
-        <item x="161"/>
-        <item x="325"/>
-        <item x="823"/>
-        <item x="611"/>
-        <item x="500"/>
-        <item x="586"/>
-        <item x="292"/>
-        <item x="223"/>
-        <item x="156"/>
-        <item x="141"/>
-        <item x="40"/>
-        <item x="503"/>
-        <item x="557"/>
-        <item x="288"/>
-        <item x="190"/>
-        <item x="613"/>
-        <item x="60"/>
-        <item x="306"/>
-        <item x="192"/>
-        <item x="526"/>
-        <item x="430"/>
-        <item x="74"/>
-        <item x="530"/>
-        <item x="754"/>
-        <item x="836"/>
-        <item x="380"/>
-        <item x="230"/>
-        <item x="253"/>
-        <item x="508"/>
-        <item x="116"/>
-        <item x="883"/>
-        <item x="841"/>
-        <item x="448"/>
-        <item x="729"/>
-        <item x="15"/>
-        <item x="20"/>
-        <item x="444"/>
-        <item x="423"/>
-        <item x="590"/>
-        <item x="996"/>
-        <item x="689"/>
-        <item x="186"/>
-        <item x="483"/>
-        <item x="951"/>
-        <item x="782"/>
-        <item x="298"/>
-        <item x="157"/>
-        <item x="629"/>
-        <item x="393"/>
-        <item x="538"/>
-        <item x="882"/>
-        <item x="910"/>
-        <item x="749"/>
-        <item x="7"/>
-        <item x="396"/>
-        <item x="171"/>
-        <item x="859"/>
-        <item x="293"/>
-        <item x="608"/>
-        <item x="89"/>
-        <item x="637"/>
-        <item x="19"/>
-        <item x="217"/>
-        <item x="463"/>
-        <item x="354"/>
-        <item x="681"/>
-        <item x="926"/>
-        <item x="660"/>
-        <item x="801"/>
-        <item x="961"/>
-        <item x="429"/>
-        <item x="886"/>
-        <item x="458"/>
-        <item x="462"/>
-        <item x="50"/>
-        <item x="616"/>
-        <item x="18"/>
-        <item x="944"/>
-        <item x="38"/>
-        <item x="599"/>
-        <item x="123"/>
-        <item x="142"/>
-        <item x="536"/>
-        <item x="582"/>
-        <item x="527"/>
-        <item x="575"/>
-        <item x="471"/>
-        <item x="329"/>
-        <item x="179"/>
-        <item x="571"/>
-        <item x="832"/>
-        <item x="541"/>
-        <item x="437"/>
-        <item x="744"/>
-        <item x="399"/>
-        <item x="238"/>
-        <item x="62"/>
-        <item x="998"/>
-        <item x="510"/>
-        <item x="609"/>
-        <item x="10"/>
-        <item x="42"/>
-        <item x="137"/>
-        <item x="573"/>
-        <item x="6"/>
-        <item x="555"/>
-        <item x="539"/>
-        <item x="583"/>
-        <item x="798"/>
-        <item x="84"/>
-        <item x="866"/>
-        <item x="937"/>
-        <item x="86"/>
-        <item x="638"/>
-        <item x="963"/>
-        <item x="949"/>
-        <item x="12"/>
-        <item x="820"/>
-        <item x="256"/>
-        <item x="650"/>
-        <item x="46"/>
-        <item x="682"/>
-        <item x="21"/>
-        <item x="409"/>
-        <item x="694"/>
-        <item x="322"/>
-        <item x="602"/>
-        <item x="742"/>
-        <item x="4"/>
-        <item x="948"/>
-        <item x="339"/>
-        <item x="985"/>
-        <item x="584"/>
-        <item x="244"/>
-        <item x="277"/>
-        <item x="900"/>
-        <item x="340"/>
-        <item x="119"/>
-        <item x="588"/>
-        <item x="811"/>
-        <item x="259"/>
-        <item x="77"/>
-        <item x="69"/>
-        <item x="373"/>
-        <item x="959"/>
-        <item x="736"/>
-        <item x="506"/>
-        <item x="767"/>
-        <item x="222"/>
-        <item x="890"/>
-        <item x="745"/>
-        <item x="580"/>
-        <item x="445"/>
-        <item x="70"/>
-        <item x="441"/>
-        <item x="388"/>
-        <item x="204"/>
-        <item x="690"/>
-        <item x="304"/>
-        <item x="927"/>
-        <item x="55"/>
-        <item x="553"/>
-        <item x="349"/>
-        <item x="188"/>
-        <item x="791"/>
-        <item x="154"/>
-        <item x="799"/>
-        <item x="498"/>
-        <item x="785"/>
-        <item x="472"/>
-        <item x="757"/>
-        <item x="178"/>
-        <item x="569"/>
-        <item x="668"/>
-        <item x="851"/>
-        <item x="897"/>
-        <item x="762"/>
-        <item x="305"/>
-        <item x="515"/>
-        <item x="174"/>
-        <item x="343"/>
-        <item x="829"/>
-        <item x="232"/>
-        <item x="720"/>
-        <item x="633"/>
-        <item x="199"/>
-        <item x="499"/>
-        <item x="620"/>
-        <item x="610"/>
-        <item x="374"/>
-        <item x="159"/>
-        <item x="313"/>
-        <item x="163"/>
-        <item x="516"/>
-        <item x="202"/>
-        <item x="834"/>
-        <item x="316"/>
-        <item x="957"/>
-        <item x="989"/>
-        <item x="289"/>
-        <item x="928"/>
-        <item x="936"/>
-        <item x="341"/>
-        <item x="724"/>
-        <item x="181"/>
-        <item x="531"/>
-        <item x="621"/>
-        <item x="494"/>
-        <item x="191"/>
-        <item x="485"/>
-        <item x="733"/>
-        <item x="303"/>
-        <item x="466"/>
-        <item x="346"/>
-        <item x="726"/>
-        <item x="333"/>
-        <item x="614"/>
-        <item x="796"/>
-        <item x="581"/>
-        <item x="709"/>
-        <item x="300"/>
-        <item x="263"/>
-        <item x="971"/>
-        <item x="878"/>
-        <item x="241"/>
-        <item x="943"/>
-        <item x="449"/>
-        <item x="440"/>
-        <item x="906"/>
-        <item x="521"/>
-        <item x="741"/>
-        <item x="972"/>
-        <item x="447"/>
-        <item x="912"/>
-        <item x="358"/>
-        <item x="924"/>
-        <item x="746"/>
-        <item x="779"/>
-        <item x="933"/>
-        <item x="145"/>
-        <item x="576"/>
-        <item x="914"/>
-        <item x="432"/>
-        <item x="540"/>
-        <item x="885"/>
-        <item x="363"/>
-        <item x="381"/>
-        <item x="228"/>
-        <item x="221"/>
-        <item x="367"/>
-        <item x="783"/>
-        <item x="595"/>
-        <item x="464"/>
-        <item x="773"/>
-        <item x="362"/>
-        <item x="414"/>
-        <item x="802"/>
-        <item x="274"/>
-        <item x="816"/>
-        <item x="239"/>
-        <item x="110"/>
-        <item x="82"/>
-        <item x="717"/>
-        <item x="134"/>
-        <item x="604"/>
-        <item x="476"/>
-        <item x="748"/>
-        <item x="143"/>
-        <item x="424"/>
-        <item x="945"/>
-        <item x="282"/>
-        <item x="880"/>
-        <item x="659"/>
-        <item x="484"/>
-        <item x="840"/>
-        <item x="789"/>
-        <item x="285"/>
-        <item x="815"/>
-        <item x="939"/>
-        <item x="934"/>
-        <item x="475"/>
-        <item x="514"/>
-        <item x="950"/>
-        <item x="88"/>
-        <item x="165"/>
-        <item x="901"/>
-        <item x="615"/>
-        <item x="491"/>
-        <item x="684"/>
-        <item x="72"/>
-        <item x="504"/>
-        <item x="94"/>
-        <item x="308"/>
-        <item x="564"/>
-        <item x="784"/>
-        <item x="665"/>
-        <item x="977"/>
-        <item x="517"/>
-        <item x="913"/>
-        <item x="281"/>
-        <item x="761"/>
-        <item x="385"/>
-        <item x="276"/>
-        <item x="335"/>
-        <item x="833"/>
-        <item x="680"/>
-        <item x="11"/>
-        <item x="245"/>
-        <item x="973"/>
-        <item x="348"/>
-        <item x="310"/>
-        <item x="457"/>
-        <item x="863"/>
-        <item x="524"/>
-        <item x="781"/>
-        <item x="278"/>
-        <item x="828"/>
-        <item x="548"/>
-        <item x="240"/>
-        <item x="480"/>
-        <item x="547"/>
-        <item x="390"/>
-        <item x="201"/>
-        <item x="607"/>
-        <item x="872"/>
-        <item x="904"/>
-        <item x="231"/>
-        <item x="743"/>
-        <item x="164"/>
-        <item x="884"/>
-        <item x="218"/>
-        <item x="843"/>
-        <item x="24"/>
-        <item x="129"/>
-        <item x="438"/>
-        <item x="574"/>
-        <item x="102"/>
-        <item x="987"/>
-        <item x="357"/>
-        <item x="467"/>
-        <item x="41"/>
-        <item x="673"/>
-        <item x="488"/>
-        <item x="195"/>
-        <item x="496"/>
-        <item x="966"/>
-        <item x="291"/>
-        <item x="808"/>
-        <item x="606"/>
-        <item x="216"/>
-        <item x="592"/>
-        <item x="657"/>
-        <item x="392"/>
-        <item x="651"/>
-        <item x="323"/>
-        <item x="284"/>
-        <item x="353"/>
-        <item x="90"/>
-        <item x="810"/>
-        <item x="275"/>
-        <item x="332"/>
-        <item x="453"/>
-        <item x="147"/>
-        <item x="411"/>
-        <item x="825"/>
-        <item x="267"/>
-        <item x="301"/>
-        <item x="208"/>
-        <item x="501"/>
-        <item x="49"/>
-        <item x="647"/>
-        <item x="431"/>
-        <item x="952"/>
-        <item x="139"/>
-        <item x="479"/>
-        <item x="672"/>
-        <item x="956"/>
-        <item x="359"/>
-        <item x="551"/>
-        <item x="535"/>
-        <item x="227"/>
-        <item x="871"/>
-        <item x="151"/>
-        <item x="294"/>
-        <item x="594"/>
-        <item x="751"/>
-        <item x="846"/>
-        <item x="184"/>
-        <item x="404"/>
-        <item x="763"/>
-        <item x="108"/>
-        <item x="670"/>
-        <item x="632"/>
-        <item x="133"/>
-        <item x="577"/>
-        <item x="723"/>
-        <item x="962"/>
-        <item x="765"/>
-        <item x="189"/>
-        <item x="286"/>
-        <item x="95"/>
-        <item x="33"/>
-        <item x="512"/>
-        <item x="378"/>
-        <item x="902"/>
-        <item x="389"/>
-        <item x="135"/>
-        <item x="624"/>
-        <item x="477"/>
-        <item x="519"/>
-        <item x="991"/>
-        <item x="509"/>
-        <item x="317"/>
-        <item x="247"/>
-        <item x="968"/>
-        <item x="361"/>
-        <item x="795"/>
-        <item x="200"/>
-        <item x="735"/>
-        <item x="892"/>
-        <item x="492"/>
-        <item x="877"/>
-        <item x="173"/>
-        <item x="150"/>
-        <item x="522"/>
-        <item x="636"/>
-        <item x="360"/>
-        <item x="368"/>
-        <item x="52"/>
-        <item x="433"/>
-        <item x="44"/>
-        <item x="806"/>
-        <item x="502"/>
-        <item x="321"/>
-        <item x="909"/>
-        <item x="700"/>
-        <item x="489"/>
-        <item x="106"/>
-        <item x="627"/>
-        <item x="780"/>
-        <item x="107"/>
-        <item x="868"/>
-        <item x="2"/>
-        <item x="495"/>
-        <item x="356"/>
-        <item x="338"/>
-        <item x="87"/>
-        <item x="273"/>
-        <item x="331"/>
-        <item x="731"/>
-        <item x="57"/>
-        <item x="831"/>
-        <item x="23"/>
-        <item x="919"/>
-        <item x="120"/>
-        <item x="460"/>
-        <item x="704"/>
-        <item x="32"/>
-        <item x="193"/>
-        <item x="663"/>
-        <item x="930"/>
-        <item x="619"/>
-        <item x="603"/>
-        <item x="118"/>
-        <item x="671"/>
-        <item x="537"/>
-        <item x="113"/>
-        <item x="235"/>
-        <item x="546"/>
-        <item x="687"/>
-        <item x="678"/>
-        <item x="320"/>
-        <item x="26"/>
-        <item x="427"/>
-        <item x="401"/>
-        <item x="567"/>
-        <item x="790"/>
-        <item x="755"/>
-        <item x="994"/>
-        <item x="631"/>
-        <item x="262"/>
-        <item x="213"/>
-        <item x="16"/>
-        <item x="852"/>
-        <item x="121"/>
-        <item x="117"/>
-        <item x="838"/>
-        <item x="251"/>
-        <item x="384"/>
-        <item x="128"/>
-        <item x="747"/>
-        <item x="8"/>
-        <item x="639"/>
-        <item x="375"/>
-        <item x="283"/>
-        <item x="125"/>
-        <item x="48"/>
-        <item x="837"/>
-        <item x="622"/>
-        <item x="206"/>
-        <item x="482"/>
-        <item x="813"/>
-        <item x="947"/>
-        <item x="474"/>
-        <item x="211"/>
-        <item x="721"/>
-        <item x="669"/>
-        <item x="146"/>
-        <item x="490"/>
-        <item x="271"/>
-        <item x="167"/>
-        <item x="692"/>
-        <item x="386"/>
-        <item x="993"/>
-        <item x="337"/>
-        <item x="9"/>
-        <item x="640"/>
-        <item x="587"/>
-        <item x="132"/>
-        <item x="413"/>
-        <item x="565"/>
-        <item x="198"/>
-        <item x="5"/>
-        <item x="895"/>
-        <item x="136"/>
-        <item x="545"/>
-        <item x="478"/>
-        <item x="794"/>
-        <item x="941"/>
-        <item x="788"/>
-        <item x="254"/>
-        <item x="318"/>
-        <item x="105"/>
-        <item x="645"/>
-        <item x="770"/>
-        <item x="486"/>
-        <item x="456"/>
-        <item x="768"/>
-        <item x="558"/>
-        <item x="664"/>
-        <item x="893"/>
-        <item x="104"/>
-        <item x="915"/>
-        <item x="566"/>
-        <item x="327"/>
-        <item x="525"/>
-        <item x="940"/>
-        <item x="229"/>
-        <item x="916"/>
-        <item x="407"/>
-        <item x="898"/>
-        <item x="387"/>
-        <item x="662"/>
-        <item x="347"/>
-        <item x="395"/>
-        <item x="505"/>
-        <item x="997"/>
-        <item x="452"/>
-        <item x="47"/>
-        <item x="296"/>
-        <item x="980"/>
-        <item x="711"/>
-        <item x="703"/>
-        <item x="257"/>
-        <item x="459"/>
-        <item x="85"/>
-        <item x="328"/>
-        <item x="372"/>
-        <item x="269"/>
-        <item x="473"/>
-        <item x="140"/>
-        <item x="187"/>
-        <item x="406"/>
-        <item x="75"/>
-        <item x="99"/>
-        <item x="740"/>
-        <item x="172"/>
-        <item x="520"/>
-        <item x="302"/>
-        <item x="714"/>
-        <item x="874"/>
-        <item x="649"/>
-        <item x="421"/>
-        <item x="428"/>
-        <item x="652"/>
-        <item x="158"/>
-        <item x="377"/>
-        <item x="297"/>
-        <item x="451"/>
-        <item x="792"/>
-        <item x="974"/>
-        <item x="419"/>
-        <item x="992"/>
-        <item x="970"/>
-        <item x="468"/>
-        <item x="324"/>
-        <item x="225"/>
-        <item x="152"/>
-        <item x="550"/>
-        <item x="857"/>
-        <item x="205"/>
-        <item x="917"/>
-        <item x="416"/>
-        <item x="0"/>
-        <item x="800"/>
-        <item x="699"/>
-        <item x="435"/>
-        <item x="676"/>
-        <item x="237"/>
-        <item x="79"/>
-        <item x="732"/>
-        <item x="931"/>
-        <item x="803"/>
-        <item x="771"/>
-        <item x="708"/>
-        <item x="827"/>
-        <item x="397"/>
-        <item x="563"/>
-        <item x="879"/>
-        <item x="986"/>
-        <item x="17"/>
-        <item x="96"/>
-        <item x="470"/>
-        <item x="455"/>
-        <item x="686"/>
-        <item x="856"/>
-        <item x="753"/>
-        <item x="722"/>
-        <item x="918"/>
-        <item x="39"/>
-        <item x="814"/>
-        <item x="53"/>
-        <item x="646"/>
-        <item x="299"/>
-        <item x="666"/>
-        <item x="896"/>
-        <item x="155"/>
-        <item x="270"/>
-        <item x="953"/>
-        <item x="822"/>
-        <item x="249"/>
-        <item x="756"/>
-        <item x="710"/>
-        <item x="319"/>
-        <item x="83"/>
-        <item x="764"/>
-        <item x="591"/>
-        <item x="718"/>
-        <item x="612"/>
-        <item x="219"/>
-        <item x="787"/>
-        <item x="398"/>
-        <item x="642"/>
-        <item x="964"/>
-        <item x="487"/>
-        <item x="71"/>
-        <item x="168"/>
-        <item x="578"/>
-        <item x="248"/>
-        <item x="695"/>
-        <item x="766"/>
-        <item x="215"/>
-        <item x="131"/>
-        <item x="307"/>
-        <item x="61"/>
-        <item x="845"/>
-        <item x="739"/>
-        <item x="752"/>
-        <item x="835"/>
-        <item x="266"/>
-        <item x="981"/>
-        <item x="942"/>
-        <item x="439"/>
-        <item x="674"/>
-        <item x="894"/>
-        <item x="812"/>
-        <item x="326"/>
-        <item x="626"/>
-        <item x="658"/>
-        <item x="58"/>
-        <item x="209"/>
-        <item x="261"/>
-        <item x="719"/>
-        <item x="183"/>
-        <item x="929"/>
-        <item x="697"/>
-        <item x="175"/>
-        <item x="528"/>
-        <item x="529"/>
-        <item x="618"/>
-        <item x="279"/>
-        <item x="14"/>
-        <item x="78"/>
-        <item x="605"/>
-        <item x="194"/>
-        <item x="403"/>
-        <item x="804"/>
-        <item x="817"/>
-        <item x="365"/>
-        <item x="706"/>
-        <item x="351"/>
-        <item x="570"/>
-        <item x="334"/>
-        <item x="226"/>
-        <item x="434"/>
-        <item x="922"/>
-        <item x="66"/>
-        <item x="617"/>
-        <item x="861"/>
-        <item x="544"/>
-        <item x="73"/>
-        <item x="661"/>
-        <item x="760"/>
-        <item x="376"/>
-        <item x="850"/>
-        <item x="250"/>
-        <item x="848"/>
-        <item x="955"/>
-        <item x="81"/>
-        <item x="418"/>
-        <item x="196"/>
-        <item x="309"/>
-        <item x="29"/>
-        <item x="860"/>
-        <item x="999"/>
-        <item x="260"/>
-        <item x="182"/>
-        <item x="907"/>
-        <item x="623"/>
-        <item x="869"/>
-        <item x="64"/>
-        <item x="197"/>
-        <item x="628"/>
-        <item x="716"/>
-        <item x="532"/>
-        <item x="648"/>
-        <item x="946"/>
-        <item x="842"/>
-        <item x="350"/>
-        <item x="109"/>
-        <item x="507"/>
-        <item x="847"/>
-        <item x="497"/>
-        <item x="797"/>
-        <item x="903"/>
-        <item x="98"/>
-        <item x="246"/>
-        <item x="853"/>
-        <item x="561"/>
-        <item x="958"/>
-        <item x="698"/>
-        <item x="382"/>
-        <item x="330"/>
-        <item x="818"/>
-        <item x="126"/>
-        <item x="80"/>
-        <item x="312"/>
-        <item x="97"/>
-        <item x="30"/>
-        <item x="870"/>
-        <item x="92"/>
-        <item x="342"/>
-        <item x="777"/>
-        <item x="203"/>
-        <item x="65"/>
-        <item x="465"/>
-        <item x="593"/>
-        <item x="889"/>
-        <item x="601"/>
-        <item x="405"/>
-        <item x="252"/>
-        <item x="975"/>
-        <item x="887"/>
-        <item x="394"/>
-        <item x="876"/>
-        <item x="990"/>
-        <item x="769"/>
-        <item x="786"/>
-        <item x="923"/>
-        <item x="210"/>
-        <item x="355"/>
-        <item x="450"/>
-        <item x="214"/>
-        <item x="534"/>
-        <item x="160"/>
-        <item x="855"/>
-        <item x="185"/>
-        <item x="844"/>
-        <item x="336"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="1"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="90">
-        <item x="17"/>
-        <item x="56"/>
-        <item x="75"/>
-        <item x="72"/>
-        <item x="0"/>
-        <item x="47"/>
-        <item x="27"/>
-        <item x="66"/>
-        <item x="51"/>
-        <item x="8"/>
-        <item x="83"/>
-        <item x="52"/>
-        <item x="50"/>
-        <item x="78"/>
-        <item x="15"/>
-        <item x="65"/>
-        <item x="29"/>
-        <item x="68"/>
-        <item x="64"/>
-        <item x="40"/>
-        <item x="18"/>
-        <item x="49"/>
-        <item x="54"/>
-        <item x="46"/>
-        <item x="25"/>
-        <item x="53"/>
-        <item x="3"/>
-        <item x="26"/>
-        <item x="71"/>
-        <item x="74"/>
-        <item x="82"/>
-        <item x="60"/>
-        <item x="30"/>
-        <item x="36"/>
-        <item x="87"/>
-        <item x="63"/>
-        <item x="10"/>
-        <item x="13"/>
-        <item x="4"/>
-        <item x="57"/>
-        <item x="34"/>
-        <item x="48"/>
-        <item x="12"/>
-        <item x="77"/>
-        <item x="44"/>
-        <item x="42"/>
-        <item x="69"/>
-        <item x="21"/>
-        <item x="67"/>
-        <item x="88"/>
-        <item x="9"/>
-        <item x="81"/>
-        <item x="70"/>
-        <item x="55"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="84"/>
-        <item x="33"/>
-        <item x="38"/>
-        <item x="59"/>
-        <item x="22"/>
-        <item x="2"/>
-        <item x="31"/>
-        <item x="19"/>
-        <item x="43"/>
-        <item x="37"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="24"/>
-        <item x="16"/>
-        <item x="41"/>
-        <item x="45"/>
-        <item x="86"/>
-        <item x="20"/>
-        <item x="32"/>
-        <item x="85"/>
-        <item x="79"/>
-        <item x="35"/>
-        <item x="80"/>
-        <item x="76"/>
-        <item x="23"/>
-        <item x="28"/>
-        <item x="62"/>
-        <item x="5"/>
-        <item x="58"/>
-        <item x="39"/>
-        <item x="61"/>
-        <item x="14"/>
-        <item x="73"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="20" showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0" countASubtotal="1">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="countA"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Payment" fld="11" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="4">
-    <chartFormat chart="7" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="11" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="11" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="11" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -41363,8 +41596,8 @@
   <data>
     <tabular pivotCacheId="161129739">
       <items count="3">
-        <i x="0" s="1"/>
-        <i x="2" s="1"/>
+        <i x="0"/>
+        <i x="2"/>
         <i x="1" s="1"/>
       </items>
     </tabular>
@@ -41444,7 +41677,7 @@
   <slicer name="Branch" xr10:uid="{B118296F-5E25-4EAA-8941-DC3A2E2264FA}" cache="Slicer_Branch" caption="Branch" rowHeight="257175"/>
   <slicer name="Customer type" xr10:uid="{81F752C6-2F8A-4BEC-B0B2-679BCA6A99FF}" cache="Slicer_Customer_type" caption="Customer type" rowHeight="257175"/>
   <slicer name="Gender" xr10:uid="{CE3DCD5A-048D-42E4-A897-96B0EB2A1B02}" cache="Slicer_Gender" caption="Gender" rowHeight="257175"/>
-  <slicer name="Payment" xr10:uid="{2B3A70FA-8948-41A2-B259-387946D6F096}" cache="Slicer_Payment" caption="Payment" startItem="1" rowHeight="257175"/>
+  <slicer name="Payment" xr10:uid="{2B3A70FA-8948-41A2-B259-387946D6F096}" cache="Slicer_Payment" caption="Payment" rowHeight="257175"/>
 </slicers>
 </file>
 
@@ -41458,11 +41691,11 @@
     <tableColumn id="4" xr3:uid="{98EC3225-A569-4C63-83DE-61F7F0D53A07}" name="Customer type"/>
     <tableColumn id="5" xr3:uid="{7B7C434A-A118-4BF3-9C74-5BEACD997C37}" name="Gender"/>
     <tableColumn id="6" xr3:uid="{84A3DC5F-72BE-43AE-A93A-DAB1A9C0750F}" name="Product line"/>
-    <tableColumn id="7" xr3:uid="{0E536871-FE70-4BC7-A887-3CB72038CB16}" name="Unit price" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{0E536871-FE70-4BC7-A887-3CB72038CB16}" name="Unit price" dataDxfId="103"/>
     <tableColumn id="8" xr3:uid="{AE09FCEA-0B63-4E03-8A2D-BEDFC0EF6347}" name="Quantity"/>
-    <tableColumn id="9" xr3:uid="{A85F0D12-DD87-4775-8199-58F671C1EE17}" name="Sales" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{1EB240C5-A8B9-4DCD-BA01-F22F4460D119}" name="Date" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{19A62CFE-CB4D-4D40-81B8-B219C657CF44}" name="Time" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{A85F0D12-DD87-4775-8199-58F671C1EE17}" name="Sales" dataDxfId="102"/>
+    <tableColumn id="10" xr3:uid="{1EB240C5-A8B9-4DCD-BA01-F22F4460D119}" name="Date" dataDxfId="101"/>
+    <tableColumn id="11" xr3:uid="{19A62CFE-CB4D-4D40-81B8-B219C657CF44}" name="Time" dataDxfId="100"/>
     <tableColumn id="12" xr3:uid="{BD23BEBD-BC0C-4483-A64E-9EF0BECABA0E}" name="Payment"/>
     <tableColumn id="13" xr3:uid="{4EC68B64-78B3-44D3-965A-F1383643ECF4}" name="cogs"/>
     <tableColumn id="14" xr3:uid="{F3EFA18A-9901-4B84-BDDD-4FBD49DC2B9E}" name="Rating"/>
@@ -41788,7 +42021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67640A84-9F9A-4CB4-9763-CB98C9BF957B}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -41824,41 +42057,41 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
-        <v>322966.74900000007</v>
+        <v>110568.7065</v>
       </c>
       <c r="B4" s="7">
-        <v>15379.368999999715</v>
+        <v>5265.1764999999577</v>
       </c>
       <c r="C4" s="13">
-        <v>1000</v>
+        <v>328</v>
       </c>
       <c r="D4" s="6">
-        <v>6.9727000000000032</v>
+        <v>7.0728658536585378</v>
       </c>
       <c r="E4" s="13">
-        <v>5510</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <f>GETPIVOTDATA("Total Sales",$A$3)</f>
-        <v>322966.74900000007</v>
+        <v>110568.7065</v>
       </c>
       <c r="B5" s="12">
         <f>GETPIVOTDATA("Total Profit ",$A$3)</f>
-        <v>15379.368999999715</v>
+        <v>5265.1764999999577</v>
       </c>
       <c r="C5">
         <f>GETPIVOTDATA("Count of Invoice ID",$A$3)</f>
-        <v>1000</v>
+        <v>328</v>
       </c>
       <c r="D5" s="6">
         <f>GETPIVOTDATA("Average Rating",$A$3)</f>
-        <v>6.9727000000000032</v>
+        <v>7.0728658536585378</v>
       </c>
       <c r="E5">
         <f>GETPIVOTDATA("Total Quantity",$A$3)</f>
-        <v>5510</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -41888,16 +42121,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B8" s="7">
-        <v>49193.739000000016</v>
+        <v>13895.553</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E8" s="7">
-        <v>5057.1605000000418</v>
+        <v>5265.1764999999577</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>1055</v>
@@ -41908,42 +42141,36 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B9" s="7">
-        <v>53861.913000000008</v>
+        <v>15761.928</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>38</v>
+        <v>1056</v>
       </c>
       <c r="E9" s="7">
-        <v>5057.0320000000356</v>
+        <v>5265.1764999999577</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>1066</v>
       </c>
       <c r="H9" s="11">
-        <v>116291.86800000005</v>
+        <v>40434.681000000004</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="B10" s="7">
-        <v>54305.894999999997</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="7">
-        <v>5265.1764999999432</v>
+        <v>16615.326000000001</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>1067</v>
       </c>
       <c r="H10" s="11">
-        <v>97219.373999999967</v>
+        <v>32934.982499999998</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -41951,33 +42178,27 @@
         <v>24</v>
       </c>
       <c r="B11" s="7">
-        <v>54337.531500000005</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E11" s="7">
-        <v>15379.369000000705</v>
+        <v>18968.974500000004</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>1068</v>
       </c>
       <c r="H11" s="11">
-        <v>109455.50700000004</v>
+        <v>37199.042999999998</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B12" s="7">
-        <v>55122.826499999996</v>
+        <v>21560.070000000003</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>1056</v>
       </c>
       <c r="H12" s="7">
-        <v>322966.74900000007</v>
+        <v>110568.7065</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -41985,7 +42206,7 @@
         <v>40</v>
       </c>
       <c r="B13" s="7">
-        <v>56144.844000000005</v>
+        <v>23766.854999999992</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -41993,7 +42214,7 @@
         <v>1056</v>
       </c>
       <c r="B14" s="7">
-        <v>322966.74900000007</v>
+        <v>110568.7065</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -42027,13 +42248,13 @@
         <v>25</v>
       </c>
       <c r="E17" s="13">
-        <v>344</v>
+        <v>124</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>16</v>
       </c>
       <c r="H17" s="11">
-        <v>164223.44400000002</v>
+        <v>56881.282499999994</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -42047,13 +42268,13 @@
         <v>29</v>
       </c>
       <c r="E18" s="13">
-        <v>311</v>
+        <v>98</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="11">
-        <v>158743.30500000005</v>
+        <v>53687.423999999999</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -42061,49 +42282,33 @@
         <v>22</v>
       </c>
       <c r="B19" s="11">
-        <v>110568.70649999994</v>
+        <v>110568.7065</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>19</v>
       </c>
       <c r="E19" s="13">
-        <v>345</v>
+        <v>106</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>1056</v>
       </c>
       <c r="H19" s="7">
-        <v>322966.74900000007</v>
+        <v>110568.7065</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="11">
-        <v>106200.37050000011</v>
+        <v>1056</v>
+      </c>
+      <c r="B20" s="7">
+        <v>110568.7065</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>1056</v>
       </c>
       <c r="E20" s="13">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="11">
-        <v>106197.67199999996</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B22" s="7">
-        <v>322966.74900000001</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
